--- a/scripts/data/50m_Femenino_Absoluto_Libre.xlsx
+++ b/scripts/data/50m_Femenino_Absoluto_Libre.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O150"/>
+  <dimension ref="A1:O154"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1071,22 +1071,22 @@
         <v>50 Libre</v>
       </c>
       <c r="C16" t="str">
-        <v>MANUELA RADEANU</v>
+        <v>MARIA ANGELES GRASSO CUENCA</v>
       </c>
       <c r="D16">
-        <v>2007</v>
+        <v>2011</v>
       </c>
       <c r="E16" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F16" t="str">
-        <v>00:00:30.82</v>
+        <v>00:00:30.53</v>
       </c>
       <c r="G16">
-        <v>450</v>
+        <v>462</v>
       </c>
       <c r="H16" s="1">
-        <v>45115.99949074074</v>
+        <v>46200.99949074074</v>
       </c>
       <c r="I16" t="str">
         <v>Deportista</v>
@@ -1098,10 +1098,10 @@
         <v>Electrónico</v>
       </c>
       <c r="L16" t="str">
-        <v>CAMPEONATO AUTONÓMICO JUNIOR Y ABSOLUTO DE VERANO 2023</v>
+        <v>CAMPEONATO AUTONOMICO INFANTIL DE VERANO DE LA C.V. 2026</v>
       </c>
       <c r="M16" t="str">
-        <v>Castellón</v>
+        <v>CASTELLON</v>
       </c>
       <c r="N16" t="str">
         <v>No</v>
@@ -1115,22 +1115,22 @@
         <v>50 Libre</v>
       </c>
       <c r="C17" t="str">
-        <v>VEGA ALCANTARA SANTA CRUZ</v>
+        <v>MANUELA RADEANU</v>
       </c>
       <c r="D17">
-        <v>2011</v>
+        <v>2007</v>
       </c>
       <c r="E17" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F17" t="str">
-        <v>00:00:30.87</v>
+        <v>00:00:30.82</v>
       </c>
       <c r="G17">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="H17" s="1">
-        <v>46046.99949074074</v>
+        <v>45115.99949074074</v>
       </c>
       <c r="I17" t="str">
         <v>Deportista</v>
@@ -1142,10 +1142,10 @@
         <v>Electrónico</v>
       </c>
       <c r="L17" t="str">
-        <v>TROFEO INTERNACIONAL XXXI MEMORIAL PASCUAL ROMAN</v>
+        <v>CAMPEONATO AUTONÓMICO JUNIOR Y ABSOLUTO DE VERANO 2023</v>
       </c>
       <c r="M17" t="str">
-        <v>Elche</v>
+        <v>Castellón</v>
       </c>
       <c r="N17" t="str">
         <v>No</v>
@@ -1159,22 +1159,22 @@
         <v>50 Libre</v>
       </c>
       <c r="C18" t="str">
-        <v>ADRIANA DIAZ CUEVAS</v>
+        <v>VEGA ALCANTARA SANTA CRUZ</v>
       </c>
       <c r="D18">
-        <v>2010</v>
+        <v>2011</v>
       </c>
       <c r="E18" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F18" t="str">
-        <v>00:00:31.03</v>
+        <v>00:00:30.87</v>
       </c>
       <c r="G18">
-        <v>440</v>
+        <v>447</v>
       </c>
       <c r="H18" s="1">
-        <v>45710.99949074074</v>
+        <v>46046.99949074074</v>
       </c>
       <c r="I18" t="str">
         <v>Deportista</v>
@@ -1186,10 +1186,10 @@
         <v>Electrónico</v>
       </c>
       <c r="L18" t="str">
-        <v>CAMPEONATO AUTONOMICO INFANTIL DE INVIERNO 2025 C.V.</v>
+        <v>TROFEO INTERNACIONAL XXXI MEMORIAL PASCUAL ROMAN</v>
       </c>
       <c r="M18" t="str">
-        <v>ELCHE</v>
+        <v>Elche</v>
       </c>
       <c r="N18" t="str">
         <v>No</v>
@@ -1203,22 +1203,22 @@
         <v>50 Libre</v>
       </c>
       <c r="C19" t="str">
-        <v>MARIA ANGELES GRASSO CUENCA</v>
+        <v>ADRIANA DIAZ CUEVAS</v>
       </c>
       <c r="D19">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="E19" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F19" t="str">
-        <v>00:00:31.09</v>
+        <v>00:00:31.03</v>
       </c>
       <c r="G19">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="H19" s="1">
-        <v>46145.99949074074</v>
+        <v>45710.99949074074</v>
       </c>
       <c r="I19" t="str">
         <v>Deportista</v>
@@ -1230,10 +1230,10 @@
         <v>Electrónico</v>
       </c>
       <c r="L19" t="str">
-        <v>XX TROFEO INTERNACIONAL IBERCAJA CIUDAD ZARAGOZA 2026 XVII MEMORIAL EDUARDO LASTRADA</v>
+        <v>CAMPEONATO AUTONOMICO INFANTIL DE INVIERNO 2025 C.V.</v>
       </c>
       <c r="M19" t="str">
-        <v>ZARAGOZA (C)</v>
+        <v>ELCHE</v>
       </c>
       <c r="N19" t="str">
         <v>No</v>
@@ -1291,22 +1291,22 @@
         <v>50 Libre</v>
       </c>
       <c r="C21" t="str">
-        <v>ROCIO MARTINEZ GONZALEZ</v>
+        <v>DARIA ILIYANOVA KIRYAKOVA</v>
       </c>
       <c r="D21">
-        <v>2011</v>
+        <v>2012</v>
       </c>
       <c r="E21" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F21" t="str">
-        <v>00:00:31.43</v>
+        <v>00:00:31.37</v>
       </c>
       <c r="G21">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="H21" s="1">
-        <v>46046.99949074074</v>
+        <v>46200.99949074074</v>
       </c>
       <c r="I21" t="str">
         <v>Deportista</v>
@@ -1318,10 +1318,10 @@
         <v>Electrónico</v>
       </c>
       <c r="L21" t="str">
-        <v>TROFEO INTERNACIONAL XXXI MEMORIAL PASCUAL ROMAN</v>
+        <v>CAMPEONATO AUTONOMICO INFANTIL DE VERANO DE LA C.V. 2026</v>
       </c>
       <c r="M21" t="str">
-        <v>Elche</v>
+        <v>CASTELLON</v>
       </c>
       <c r="N21" t="str">
         <v>No</v>
@@ -1335,22 +1335,22 @@
         <v>50 Libre</v>
       </c>
       <c r="C22" t="str">
-        <v>EVE FRENCH</v>
+        <v>ROCIO MARTINEZ GONZALEZ</v>
       </c>
       <c r="D22">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="E22" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F22" t="str">
-        <v>00:00:31.47</v>
+        <v>00:00:31.43</v>
       </c>
       <c r="G22">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="H22" s="1">
-        <v>46171.99949074074</v>
+        <v>46046.99949074074</v>
       </c>
       <c r="I22" t="str">
         <v>Deportista</v>
@@ -1359,13 +1359,13 @@
         <v>50m</v>
       </c>
       <c r="K22" t="str">
-        <v>Manual</v>
+        <v>Electrónico</v>
       </c>
       <c r="L22" t="str">
-        <v>LVI TROFEU SANT PASCUAL XXXVII MEMORIAL JOSE VICENTE MARTI BARRACHINA</v>
+        <v>TROFEO INTERNACIONAL XXXI MEMORIAL PASCUAL ROMAN</v>
       </c>
       <c r="M22" t="str">
-        <v>Vila-Real</v>
+        <v>Elche</v>
       </c>
       <c r="N22" t="str">
         <v>No</v>
@@ -1379,22 +1379,22 @@
         <v>50 Libre</v>
       </c>
       <c r="C23" t="str">
-        <v>SOFIA CALABUIG MARTINEZ</v>
+        <v>EVE FRENCH</v>
       </c>
       <c r="D23">
-        <v>2011</v>
+        <v>2009</v>
       </c>
       <c r="E23" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F23" t="str">
-        <v>00:00:31.48</v>
+        <v>00:00:31.47</v>
       </c>
       <c r="G23">
         <v>422</v>
       </c>
       <c r="H23" s="1">
-        <v>46081.99949074074</v>
+        <v>46171.99949074074</v>
       </c>
       <c r="I23" t="str">
         <v>Deportista</v>
@@ -1403,16 +1403,16 @@
         <v>50m</v>
       </c>
       <c r="K23" t="str">
-        <v>Electrónico</v>
+        <v>Manual</v>
       </c>
       <c r="L23" t="str">
-        <v>CAMPEONATO AUTONOMICO INFANTIL DE INVIERNO 2026</v>
+        <v>LVI TROFEU SANT PASCUAL XXXVII MEMORIAL JOSE VICENTE MARTI BARRACHINA</v>
       </c>
       <c r="M23" t="str">
-        <v>CASTELLÓN</v>
+        <v>Vila-Real</v>
       </c>
       <c r="N23" t="str">
-        <v>Sí</v>
+        <v>No</v>
       </c>
     </row>
     <row r="24">
@@ -1423,22 +1423,22 @@
         <v>50 Libre</v>
       </c>
       <c r="C24" t="str">
-        <v>CAMILA GUEVARA PEROZO</v>
+        <v>SOFIA CALABUIG MARTINEZ</v>
       </c>
       <c r="D24">
-        <v>2010</v>
+        <v>2011</v>
       </c>
       <c r="E24" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F24" t="str">
-        <v>00:00:31.66</v>
+        <v>00:00:31.48</v>
       </c>
       <c r="G24">
-        <v>415</v>
+        <v>422</v>
       </c>
       <c r="H24" s="1">
-        <v>45710.99949074074</v>
+        <v>46081.99949074074</v>
       </c>
       <c r="I24" t="str">
         <v>Deportista</v>
@@ -1450,13 +1450,13 @@
         <v>Electrónico</v>
       </c>
       <c r="L24" t="str">
-        <v>CAMPEONATO AUTONOMICO INFANTIL DE INVIERNO 2025 C.V.</v>
+        <v>CAMPEONATO AUTONOMICO INFANTIL DE INVIERNO 2026</v>
       </c>
       <c r="M24" t="str">
-        <v>ELCHE</v>
+        <v>CASTELLÓN</v>
       </c>
       <c r="N24" t="str">
-        <v>No</v>
+        <v>Sí</v>
       </c>
     </row>
     <row r="25">
@@ -1467,7 +1467,7 @@
         <v>50 Libre</v>
       </c>
       <c r="C25" t="str">
-        <v>PAOLA MEIJIDE VILLANUEVA</v>
+        <v>CAMILA GUEVARA PEROZO</v>
       </c>
       <c r="D25">
         <v>2010</v>
@@ -1476,13 +1476,13 @@
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F25" t="str">
-        <v>00:00:31.90</v>
+        <v>00:00:31.66</v>
       </c>
       <c r="G25">
-        <v>405</v>
+        <v>415</v>
       </c>
       <c r="H25" s="1">
-        <v>46171.99949074074</v>
+        <v>45710.99949074074</v>
       </c>
       <c r="I25" t="str">
         <v>Deportista</v>
@@ -1491,13 +1491,13 @@
         <v>50m</v>
       </c>
       <c r="K25" t="str">
-        <v>Manual</v>
+        <v>Electrónico</v>
       </c>
       <c r="L25" t="str">
-        <v>LVI TROFEU SANT PASCUAL XXXVII MEMORIAL JOSE VICENTE MARTI BARRACHINA</v>
+        <v>CAMPEONATO AUTONOMICO INFANTIL DE INVIERNO 2025 C.V.</v>
       </c>
       <c r="M25" t="str">
-        <v>Vila-Real</v>
+        <v>ELCHE</v>
       </c>
       <c r="N25" t="str">
         <v>No</v>
@@ -1511,22 +1511,22 @@
         <v>50 Libre</v>
       </c>
       <c r="C26" t="str">
-        <v>JUDITH HERGUETA VICIANO</v>
+        <v>PAOLA MEIJIDE VILLANUEVA</v>
       </c>
       <c r="D26">
-        <v>2008</v>
+        <v>2010</v>
       </c>
       <c r="E26" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F26" t="str">
-        <v>00:00:31.97</v>
+        <v>00:00:31.90</v>
       </c>
       <c r="G26">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="H26" s="1">
-        <v>45801.99949074074</v>
+        <v>46171.99949074074</v>
       </c>
       <c r="I26" t="str">
         <v>Deportista</v>
@@ -1535,16 +1535,16 @@
         <v>50m</v>
       </c>
       <c r="K26" t="str">
-        <v>Electrónico</v>
+        <v>Manual</v>
       </c>
       <c r="L26" t="str">
-        <v>CAMPEONATO AUTONOMICO JUNIOR Y ABSOLUTO DE VERANO 2025</v>
+        <v>LVI TROFEU SANT PASCUAL XXXVII MEMORIAL JOSE VICENTE MARTI BARRACHINA</v>
       </c>
       <c r="M26" t="str">
-        <v>Castellón</v>
+        <v>Vila-Real</v>
       </c>
       <c r="N26" t="str">
-        <v>Sí</v>
+        <v>No</v>
       </c>
     </row>
     <row r="27">
@@ -1555,22 +1555,22 @@
         <v>50 Libre</v>
       </c>
       <c r="C27" t="str">
-        <v>MARTINA GOMEZ GONZALEZ</v>
+        <v>JUDITH HERGUETA VICIANO</v>
       </c>
       <c r="D27">
-        <v>2007</v>
+        <v>2008</v>
       </c>
       <c r="E27" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F27" t="str">
-        <v>00:00:31.99</v>
+        <v>00:00:31.97</v>
       </c>
       <c r="G27">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="H27" s="1">
-        <v>45116.99949074074</v>
+        <v>45801.99949074074</v>
       </c>
       <c r="I27" t="str">
         <v>Deportista</v>
@@ -1582,13 +1582,13 @@
         <v>Electrónico</v>
       </c>
       <c r="L27" t="str">
-        <v>CAMPEONATO AUTONÓMICO JUNIOR Y ABSOLUTO DE VERANO 2023</v>
+        <v>CAMPEONATO AUTONOMICO JUNIOR Y ABSOLUTO DE VERANO 2025</v>
       </c>
       <c r="M27" t="str">
         <v>Castellón</v>
       </c>
       <c r="N27" t="str">
-        <v>No</v>
+        <v>Sí</v>
       </c>
     </row>
     <row r="28">
@@ -1599,22 +1599,22 @@
         <v>50 Libre</v>
       </c>
       <c r="C28" t="str">
-        <v>ARIADNA MANZANEDA GARCIA</v>
+        <v>MARTINA GOMEZ GONZALEZ</v>
       </c>
       <c r="D28">
-        <v>2012</v>
+        <v>2007</v>
       </c>
       <c r="E28" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F28" t="str">
-        <v>00:00:32.65</v>
+        <v>00:00:31.99</v>
       </c>
       <c r="G28">
-        <v>378</v>
+        <v>402</v>
       </c>
       <c r="H28" s="1">
-        <v>46171.99949074074</v>
+        <v>45116.99949074074</v>
       </c>
       <c r="I28" t="str">
         <v>Deportista</v>
@@ -1623,13 +1623,13 @@
         <v>50m</v>
       </c>
       <c r="K28" t="str">
-        <v>Manual</v>
+        <v>Electrónico</v>
       </c>
       <c r="L28" t="str">
-        <v>LVI TROFEU SANT PASCUAL XXXVII MEMORIAL JOSE VICENTE MARTI BARRACHINA</v>
+        <v>CAMPEONATO AUTONÓMICO JUNIOR Y ABSOLUTO DE VERANO 2023</v>
       </c>
       <c r="M28" t="str">
-        <v>Vila-Real</v>
+        <v>Castellón</v>
       </c>
       <c r="N28" t="str">
         <v>No</v>
@@ -1643,22 +1643,22 @@
         <v>50 Libre</v>
       </c>
       <c r="C29" t="str">
-        <v>ISABEL MORAGUES GINER</v>
+        <v>ARIADNA MANZANEDA GARCIA</v>
       </c>
       <c r="D29">
-        <v>2005</v>
+        <v>2012</v>
       </c>
       <c r="E29" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F29" t="str">
-        <v>00:00:32.71</v>
+        <v>00:00:32.65</v>
       </c>
       <c r="G29">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="H29" s="1">
-        <v>45683.99949074074</v>
+        <v>46171.99949074074</v>
       </c>
       <c r="I29" t="str">
         <v>Deportista</v>
@@ -1667,16 +1667,16 @@
         <v>50m</v>
       </c>
       <c r="K29" t="str">
-        <v>Electrónico</v>
+        <v>Manual</v>
       </c>
       <c r="L29" t="str">
-        <v>XXX MEMORIAL PASCUAL ROMAN</v>
+        <v>LVI TROFEU SANT PASCUAL XXXVII MEMORIAL JOSE VICENTE MARTI BARRACHINA</v>
       </c>
       <c r="M29" t="str">
-        <v>Elche</v>
+        <v>Vila-Real</v>
       </c>
       <c r="N29" t="str">
-        <v>Sí</v>
+        <v>No</v>
       </c>
     </row>
     <row r="30">
@@ -1687,22 +1687,22 @@
         <v>50 Libre</v>
       </c>
       <c r="C30" t="str">
-        <v>LARA VILLAESCUSA OROZCO</v>
+        <v>ISABEL MORAGUES GINER</v>
       </c>
       <c r="D30">
-        <v>2012</v>
+        <v>2005</v>
       </c>
       <c r="E30" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F30" t="str">
-        <v>00:00:32.80</v>
+        <v>00:00:32.71</v>
       </c>
       <c r="G30">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="H30" s="1">
-        <v>46081.99949074074</v>
+        <v>45683.99949074074</v>
       </c>
       <c r="I30" t="str">
         <v>Deportista</v>
@@ -1714,13 +1714,13 @@
         <v>Electrónico</v>
       </c>
       <c r="L30" t="str">
-        <v>CAMPEONATO AUTONOMICO INFANTIL DE INVIERNO 2026</v>
+        <v>XXX MEMORIAL PASCUAL ROMAN</v>
       </c>
       <c r="M30" t="str">
-        <v>CASTELLÓN</v>
+        <v>Elche</v>
       </c>
       <c r="N30" t="str">
-        <v>No</v>
+        <v>Sí</v>
       </c>
     </row>
     <row r="31">
@@ -1731,22 +1731,22 @@
         <v>50 Libre</v>
       </c>
       <c r="C31" t="str">
-        <v>MARIA MENDOZA GOMEZ</v>
+        <v>LARA VILLAESCUSA OROZCO</v>
       </c>
       <c r="D31">
-        <v>2003</v>
+        <v>2012</v>
       </c>
       <c r="E31" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F31" t="str">
-        <v>00:00:32.83</v>
+        <v>00:00:32.80</v>
       </c>
       <c r="G31">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="H31" s="1">
-        <v>43267.99949074074</v>
+        <v>46081.99949074074</v>
       </c>
       <c r="I31" t="str">
         <v>Deportista</v>
@@ -1758,10 +1758,10 @@
         <v>Electrónico</v>
       </c>
       <c r="L31" t="str">
-        <v>VII TROFEO REAL CLUB NATACION DELFIN</v>
+        <v>CAMPEONATO AUTONOMICO INFANTIL DE INVIERNO 2026</v>
       </c>
       <c r="M31" t="str">
-        <v>PARQUE OESTE</v>
+        <v>CASTELLÓN</v>
       </c>
       <c r="N31" t="str">
         <v>No</v>
@@ -1775,22 +1775,22 @@
         <v>50 Libre</v>
       </c>
       <c r="C32" t="str">
-        <v>DARIS IVANOVA STOYANOVA</v>
+        <v>MARIA MENDOZA GOMEZ</v>
       </c>
       <c r="D32">
-        <v>2011</v>
+        <v>2003</v>
       </c>
       <c r="E32" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F32" t="str">
-        <v>00:00:32.85</v>
+        <v>00:00:32.83</v>
       </c>
       <c r="G32">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="H32" s="1">
-        <v>46171.99949074074</v>
+        <v>43267.99949074074</v>
       </c>
       <c r="I32" t="str">
         <v>Deportista</v>
@@ -1799,13 +1799,13 @@
         <v>50m</v>
       </c>
       <c r="K32" t="str">
-        <v>Manual</v>
+        <v>Electrónico</v>
       </c>
       <c r="L32" t="str">
-        <v>LVI TROFEU SANT PASCUAL XXXVII MEMORIAL JOSE VICENTE MARTI BARRACHINA</v>
+        <v>VII TROFEO REAL CLUB NATACION DELFIN</v>
       </c>
       <c r="M32" t="str">
-        <v>Vila-Real</v>
+        <v>PARQUE OESTE</v>
       </c>
       <c r="N32" t="str">
         <v>No</v>
@@ -1819,22 +1819,22 @@
         <v>50 Libre</v>
       </c>
       <c r="C33" t="str">
-        <v>CARLA MARTINEZ MARTINEZ</v>
+        <v>DARIS IVANOVA STOYANOVA</v>
       </c>
       <c r="D33">
-        <v>2003</v>
+        <v>2011</v>
       </c>
       <c r="E33" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F33" t="str">
-        <v>00:00:32.92</v>
+        <v>00:00:32.85</v>
       </c>
       <c r="G33">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="H33" s="1">
-        <v>43631.99949074074</v>
+        <v>46171.99949074074</v>
       </c>
       <c r="I33" t="str">
         <v>Deportista</v>
@@ -1843,13 +1843,13 @@
         <v>50m</v>
       </c>
       <c r="K33" t="str">
-        <v>Electrónico</v>
+        <v>Manual</v>
       </c>
       <c r="L33" t="str">
-        <v>VIII Trofeo Real Club Natación Delfín-Control Calendario Único</v>
+        <v>LVI TROFEU SANT PASCUAL XXXVII MEMORIAL JOSE VICENTE MARTI BARRACHINA</v>
       </c>
       <c r="M33" t="str">
-        <v>Valencia</v>
+        <v>Vila-Real</v>
       </c>
       <c r="N33" t="str">
         <v>No</v>
@@ -1863,22 +1863,22 @@
         <v>50 Libre</v>
       </c>
       <c r="C34" t="str">
-        <v>LAURA VILA ALZAMORA</v>
+        <v>CARLA MARTINEZ MARTINEZ</v>
       </c>
       <c r="D34">
-        <v>2005</v>
+        <v>2003</v>
       </c>
       <c r="E34" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F34" t="str">
-        <v>00:00:33.11</v>
+        <v>00:00:32.92</v>
       </c>
       <c r="G34">
-        <v>363</v>
+        <v>369</v>
       </c>
       <c r="H34" s="1">
-        <v>44366.99949074074</v>
+        <v>43631.99949074074</v>
       </c>
       <c r="I34" t="str">
         <v>Deportista</v>
@@ -1887,13 +1887,13 @@
         <v>50m</v>
       </c>
       <c r="K34" t="str">
-        <v>Manual</v>
+        <v>Electrónico</v>
       </c>
       <c r="L34" t="str">
-        <v>PRUEBAS DE ACCESO AUTONÓMICO INFANTIL Y MAYORES 3 CASTELLON</v>
+        <v>VIII Trofeo Real Club Natación Delfín-Control Calendario Único</v>
       </c>
       <c r="M34" t="str">
-        <v>CASTELLON</v>
+        <v>Valencia</v>
       </c>
       <c r="N34" t="str">
         <v>No</v>
@@ -1907,22 +1907,22 @@
         <v>50 Libre</v>
       </c>
       <c r="C35" t="str">
-        <v>CLAUDIA LATORRE MARTIN</v>
+        <v>LAURA VILA ALZAMORA</v>
       </c>
       <c r="D35">
-        <v>2009</v>
+        <v>2005</v>
       </c>
       <c r="E35" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F35" t="str">
-        <v>00:00:33.28</v>
+        <v>00:00:33.11</v>
       </c>
       <c r="G35">
-        <v>357</v>
+        <v>363</v>
       </c>
       <c r="H35" s="1">
-        <v>45472.99949074074</v>
+        <v>44366.99949074074</v>
       </c>
       <c r="I35" t="str">
         <v>Deportista</v>
@@ -1931,13 +1931,13 @@
         <v>50m</v>
       </c>
       <c r="K35" t="str">
-        <v>Electrónico</v>
+        <v>Manual</v>
       </c>
       <c r="L35" t="str">
-        <v>Autonomico Infantil de Verano</v>
+        <v>PRUEBAS DE ACCESO AUTONÓMICO INFANTIL Y MAYORES 3 CASTELLON</v>
       </c>
       <c r="M35" t="str">
-        <v>Sedavi(Valencia)</v>
+        <v>CASTELLON</v>
       </c>
       <c r="N35" t="str">
         <v>No</v>
@@ -1951,22 +1951,22 @@
         <v>50 Libre</v>
       </c>
       <c r="C36" t="str">
-        <v>IRENE TAMARIT MUNERA</v>
+        <v>CLAUDIA LATORRE MARTIN</v>
       </c>
       <c r="D36">
-        <v>2008</v>
+        <v>2009</v>
       </c>
       <c r="E36" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F36" t="str">
-        <v>00:00:33.39</v>
+        <v>00:00:33.28</v>
       </c>
       <c r="G36">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="H36" s="1">
-        <v>45094.99949074074</v>
+        <v>45472.99949074074</v>
       </c>
       <c r="I36" t="str">
         <v>Deportista</v>
@@ -1978,10 +1978,10 @@
         <v>Electrónico</v>
       </c>
       <c r="L36" t="str">
-        <v>I Trofeo Federación 226ERS piscina 50m</v>
+        <v>Autonomico Infantil de Verano</v>
       </c>
       <c r="M36" t="str">
-        <v>Castellón</v>
+        <v>Sedavi(Valencia)</v>
       </c>
       <c r="N36" t="str">
         <v>No</v>
@@ -1995,22 +1995,22 @@
         <v>50 Libre</v>
       </c>
       <c r="C37" t="str">
-        <v>ALICIA FERNANDEZ CARO</v>
+        <v>IRENE TAMARIT MUNERA</v>
       </c>
       <c r="D37">
-        <v>2012</v>
+        <v>2008</v>
       </c>
       <c r="E37" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F37" t="str">
-        <v>00:00:33.62</v>
+        <v>00:00:33.39</v>
       </c>
       <c r="G37">
-        <v>346</v>
+        <v>354</v>
       </c>
       <c r="H37" s="1">
-        <v>46171.99949074074</v>
+        <v>45094.99949074074</v>
       </c>
       <c r="I37" t="str">
         <v>Deportista</v>
@@ -2019,13 +2019,13 @@
         <v>50m</v>
       </c>
       <c r="K37" t="str">
-        <v>Manual</v>
+        <v>Electrónico</v>
       </c>
       <c r="L37" t="str">
-        <v>LVI TROFEU SANT PASCUAL XXXVII MEMORIAL JOSE VICENTE MARTI BARRACHINA</v>
+        <v>I Trofeo Federación 226ERS piscina 50m</v>
       </c>
       <c r="M37" t="str">
-        <v>Vila-Real</v>
+        <v>Castellón</v>
       </c>
       <c r="N37" t="str">
         <v>No</v>
@@ -2039,22 +2039,22 @@
         <v>50 Libre</v>
       </c>
       <c r="C38" t="str">
-        <v>CELIA PARDO BARRIO</v>
+        <v>ALICIA FERNANDEZ CARO</v>
       </c>
       <c r="D38">
-        <v>2000</v>
+        <v>2012</v>
       </c>
       <c r="E38" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F38" t="str">
-        <v>00:00:34.09</v>
+        <v>00:00:33.62</v>
       </c>
       <c r="G38">
-        <v>332</v>
+        <v>346</v>
       </c>
       <c r="H38" s="1">
-        <v>42708.99949074074</v>
+        <v>46171.99949074074</v>
       </c>
       <c r="I38" t="str">
         <v>Deportista</v>
@@ -2063,13 +2063,13 @@
         <v>50m</v>
       </c>
       <c r="K38" t="str">
-        <v>Electrónico</v>
+        <v>Manual</v>
       </c>
       <c r="L38" t="str">
-        <v>TROFEO CASTALIA</v>
+        <v>LVI TROFEU SANT PASCUAL XXXVII MEMORIAL JOSE VICENTE MARTI BARRACHINA</v>
       </c>
       <c r="M38" t="str">
-        <v>CASTELLÓN</v>
+        <v>Vila-Real</v>
       </c>
       <c r="N38" t="str">
         <v>No</v>
@@ -2083,22 +2083,22 @@
         <v>50 Libre</v>
       </c>
       <c r="C39" t="str">
-        <v>JULIA ALCAIDE CATALA</v>
+        <v>CELIA PARDO BARRIO</v>
       </c>
       <c r="D39">
-        <v>2010</v>
+        <v>2000</v>
       </c>
       <c r="E39" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F39" t="str">
-        <v>00:00:34.56</v>
+        <v>00:00:34.09</v>
       </c>
       <c r="G39">
-        <v>319</v>
+        <v>332</v>
       </c>
       <c r="H39" s="1">
-        <v>46171.99949074074</v>
+        <v>42708.99949074074</v>
       </c>
       <c r="I39" t="str">
         <v>Deportista</v>
@@ -2107,13 +2107,13 @@
         <v>50m</v>
       </c>
       <c r="K39" t="str">
-        <v>Manual</v>
+        <v>Electrónico</v>
       </c>
       <c r="L39" t="str">
-        <v>LVI TROFEU SANT PASCUAL XXXVII MEMORIAL JOSE VICENTE MARTI BARRACHINA</v>
+        <v>TROFEO CASTALIA</v>
       </c>
       <c r="M39" t="str">
-        <v>Vila-Real</v>
+        <v>CASTELLÓN</v>
       </c>
       <c r="N39" t="str">
         <v>No</v>
@@ -2127,22 +2127,22 @@
         <v>50 Libre</v>
       </c>
       <c r="C40" t="str">
-        <v>ALESSIA PAFUNDI</v>
+        <v>JULIA ALCAIDE CATALA</v>
       </c>
       <c r="D40">
-        <v>2000</v>
+        <v>2010</v>
       </c>
       <c r="E40" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F40" t="str">
-        <v>00:00:34.63</v>
+        <v>00:00:34.56</v>
       </c>
       <c r="G40">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="H40" s="1">
-        <v>42708.99949074074</v>
+        <v>46171.99949074074</v>
       </c>
       <c r="I40" t="str">
         <v>Deportista</v>
@@ -2151,13 +2151,13 @@
         <v>50m</v>
       </c>
       <c r="K40" t="str">
-        <v>Electrónico</v>
+        <v>Manual</v>
       </c>
       <c r="L40" t="str">
-        <v>TROFEO CASTALIA</v>
+        <v>LVI TROFEU SANT PASCUAL XXXVII MEMORIAL JOSE VICENTE MARTI BARRACHINA</v>
       </c>
       <c r="M40" t="str">
-        <v>CASTELLÓN</v>
+        <v>Vila-Real</v>
       </c>
       <c r="N40" t="str">
         <v>No</v>
@@ -2171,22 +2171,22 @@
         <v>50 Libre</v>
       </c>
       <c r="C41" t="str">
-        <v>VERONICA MARIA GONZALEZ RUIZ</v>
+        <v>ALESSIA PAFUNDI</v>
       </c>
       <c r="D41">
-        <v>2006</v>
+        <v>2000</v>
       </c>
       <c r="E41" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F41" t="str">
-        <v>00:00:35.02</v>
+        <v>00:00:34.63</v>
       </c>
       <c r="G41">
-        <v>306</v>
+        <v>317</v>
       </c>
       <c r="H41" s="1">
-        <v>44709.99949074074</v>
+        <v>42708.99949074074</v>
       </c>
       <c r="I41" t="str">
         <v>Deportista</v>
@@ -2195,13 +2195,13 @@
         <v>50m</v>
       </c>
       <c r="K41" t="str">
-        <v>Manual</v>
+        <v>Electrónico</v>
       </c>
       <c r="L41" t="str">
-        <v>Control Libre Infantil y 7ª Control Junior y Absoluto Valencia</v>
+        <v>TROFEO CASTALIA</v>
       </c>
       <c r="M41" t="str">
-        <v>Sedavi</v>
+        <v>CASTELLÓN</v>
       </c>
       <c r="N41" t="str">
         <v>No</v>
@@ -2215,22 +2215,22 @@
         <v>50 Libre</v>
       </c>
       <c r="C42" t="str">
-        <v>ALBA FORNES GALINDO</v>
+        <v>VERONICA MARIA GONZALEZ RUIZ</v>
       </c>
       <c r="D42">
-        <v>2011</v>
+        <v>2006</v>
       </c>
       <c r="E42" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F42" t="str">
-        <v>00:00:35.20</v>
+        <v>00:00:35.02</v>
       </c>
       <c r="G42">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="H42" s="1">
-        <v>46145.99949074074</v>
+        <v>44709.99949074074</v>
       </c>
       <c r="I42" t="str">
         <v>Deportista</v>
@@ -2239,13 +2239,13 @@
         <v>50m</v>
       </c>
       <c r="K42" t="str">
-        <v>Electrónico</v>
+        <v>Manual</v>
       </c>
       <c r="L42" t="str">
-        <v>XX TROFEO INTERNACIONAL IBERCAJA CIUDAD ZARAGOZA 2026 XVII MEMORIAL EDUARDO LASTRADA</v>
+        <v>Control Libre Infantil y 7ª Control Junior y Absoluto Valencia</v>
       </c>
       <c r="M42" t="str">
-        <v>ZARAGOZA (C)</v>
+        <v>Sedavi</v>
       </c>
       <c r="N42" t="str">
         <v>No</v>
@@ -2259,22 +2259,22 @@
         <v>50 Libre</v>
       </c>
       <c r="C43" t="str">
-        <v>INGRID MONTALVA TERCERO</v>
+        <v>ALBA FORNES GALINDO</v>
       </c>
       <c r="D43">
-        <v>2008</v>
+        <v>2011</v>
       </c>
       <c r="E43" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F43" t="str">
-        <v>00:00:35.70</v>
+        <v>00:00:35.20</v>
       </c>
       <c r="G43">
-        <v>289</v>
+        <v>302</v>
       </c>
       <c r="H43" s="1">
-        <v>44709.99949074074</v>
+        <v>46145.99949074074</v>
       </c>
       <c r="I43" t="str">
         <v>Deportista</v>
@@ -2283,13 +2283,13 @@
         <v>50m</v>
       </c>
       <c r="K43" t="str">
-        <v>Manual</v>
+        <v>Electrónico</v>
       </c>
       <c r="L43" t="str">
-        <v>Control Libre Infantil y 7ª Control Junior y Absoluto Valencia</v>
+        <v>XX TROFEO INTERNACIONAL IBERCAJA CIUDAD ZARAGOZA 2026 XVII MEMORIAL EDUARDO LASTRADA</v>
       </c>
       <c r="M43" t="str">
-        <v>Sedavi</v>
+        <v>ZARAGOZA (C)</v>
       </c>
       <c r="N43" t="str">
         <v>No</v>
@@ -2303,22 +2303,22 @@
         <v>50 Libre</v>
       </c>
       <c r="C44" t="str">
-        <v>BLANCA OCHOA ARENAS</v>
+        <v>INGRID MONTALVA TERCERO</v>
       </c>
       <c r="D44">
-        <v>2000</v>
+        <v>2008</v>
       </c>
       <c r="E44" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F44" t="str">
-        <v>00:00:36.10</v>
+        <v>00:00:35.70</v>
       </c>
       <c r="G44">
-        <v>280</v>
+        <v>289</v>
       </c>
       <c r="H44" s="1">
-        <v>42708.99949074074</v>
+        <v>44709.99949074074</v>
       </c>
       <c r="I44" t="str">
         <v>Deportista</v>
@@ -2327,13 +2327,13 @@
         <v>50m</v>
       </c>
       <c r="K44" t="str">
-        <v>Electrónico</v>
+        <v>Manual</v>
       </c>
       <c r="L44" t="str">
-        <v>TROFEO CASTALIA</v>
+        <v>Control Libre Infantil y 7ª Control Junior y Absoluto Valencia</v>
       </c>
       <c r="M44" t="str">
-        <v>CASTELLÓN</v>
+        <v>Sedavi</v>
       </c>
       <c r="N44" t="str">
         <v>No</v>
@@ -2347,22 +2347,22 @@
         <v>50 Libre</v>
       </c>
       <c r="C45" t="str">
-        <v>SANDRA DOMINGUEZ VALERO</v>
+        <v>BLANCA OCHOA ARENAS</v>
       </c>
       <c r="D45">
-        <v>2007</v>
+        <v>2000</v>
       </c>
       <c r="E45" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F45" t="str">
-        <v>00:00:36.72</v>
+        <v>00:00:36.10</v>
       </c>
       <c r="G45">
-        <v>266</v>
+        <v>280</v>
       </c>
       <c r="H45" s="1">
-        <v>44709.99949074074</v>
+        <v>42708.99949074074</v>
       </c>
       <c r="I45" t="str">
         <v>Deportista</v>
@@ -2371,13 +2371,13 @@
         <v>50m</v>
       </c>
       <c r="K45" t="str">
-        <v>Manual</v>
+        <v>Electrónico</v>
       </c>
       <c r="L45" t="str">
-        <v>Control Libre Infantil y 7ª Control Junior y Absoluto Valencia</v>
+        <v>TROFEO CASTALIA</v>
       </c>
       <c r="M45" t="str">
-        <v>Sedavi</v>
+        <v>CASTELLÓN</v>
       </c>
       <c r="N45" t="str">
         <v>No</v>
@@ -2391,7 +2391,7 @@
         <v>50 Libre</v>
       </c>
       <c r="C46" t="str">
-        <v>VALERIA RUIZ ORTIZ</v>
+        <v>SANDRA DOMINGUEZ VALERO</v>
       </c>
       <c r="D46">
         <v>2007</v>
@@ -2400,13 +2400,13 @@
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F46" t="str">
-        <v>00:00:37.71</v>
+        <v>00:00:36.72</v>
       </c>
       <c r="G46">
-        <v>245</v>
+        <v>266</v>
       </c>
       <c r="H46" s="1">
-        <v>44612.99949074074</v>
+        <v>44709.99949074074</v>
       </c>
       <c r="I46" t="str">
         <v>Deportista</v>
@@ -2418,10 +2418,10 @@
         <v>Manual</v>
       </c>
       <c r="L46" t="str">
-        <v>4º Control Infantil Junior y Absoluto Castellón</v>
+        <v>Control Libre Infantil y 7ª Control Junior y Absoluto Valencia</v>
       </c>
       <c r="M46" t="str">
-        <v>Castellón</v>
+        <v>Sedavi</v>
       </c>
       <c r="N46" t="str">
         <v>No</v>
@@ -2435,7 +2435,7 @@
         <v>50 Libre</v>
       </c>
       <c r="C47" t="str">
-        <v>AINOHA MONASTERIO BANEGA</v>
+        <v>VALERIA RUIZ ORTIZ</v>
       </c>
       <c r="D47">
         <v>2007</v>
@@ -2444,10 +2444,10 @@
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F47" t="str">
-        <v>00:00:40.15</v>
+        <v>00:00:37.71</v>
       </c>
       <c r="G47">
-        <v>203</v>
+        <v>245</v>
       </c>
       <c r="H47" s="1">
         <v>44612.99949074074</v>
@@ -2479,22 +2479,22 @@
         <v>50 Libre</v>
       </c>
       <c r="C48" t="str">
-        <v>ROSA MARIA YEPES GARCIA</v>
+        <v>AINOHA MONASTERIO BANEGA</v>
       </c>
       <c r="D48">
-        <v>2006</v>
+        <v>2007</v>
       </c>
       <c r="E48" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F48" t="str">
-        <v>00:00:41.57</v>
+        <v>00:00:40.15</v>
       </c>
       <c r="G48">
-        <v>183</v>
+        <v>203</v>
       </c>
       <c r="H48" s="1">
-        <v>44709.99949074074</v>
+        <v>44612.99949074074</v>
       </c>
       <c r="I48" t="str">
         <v>Deportista</v>
@@ -2506,10 +2506,10 @@
         <v>Manual</v>
       </c>
       <c r="L48" t="str">
-        <v>Control Libre Infantil y 7ª Control Junior y Absoluto Valencia</v>
+        <v>4º Control Infantil Junior y Absoluto Castellón</v>
       </c>
       <c r="M48" t="str">
-        <v>Sedavi</v>
+        <v>Castellón</v>
       </c>
       <c r="N48" t="str">
         <v>No</v>
@@ -2523,22 +2523,22 @@
         <v>50 Libre</v>
       </c>
       <c r="C49" t="str">
-        <v>ZULEMA VIDAL HERRERO</v>
+        <v>ROSA MARIA YEPES GARCIA</v>
       </c>
       <c r="D49">
-        <v>1998</v>
+        <v>2006</v>
       </c>
       <c r="E49" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F49" t="str">
-        <v>00:00:45.28</v>
+        <v>00:00:41.57</v>
       </c>
       <c r="G49">
-        <v>142</v>
+        <v>183</v>
       </c>
       <c r="H49" s="1">
-        <v>42539.99949074074</v>
+        <v>44709.99949074074</v>
       </c>
       <c r="I49" t="str">
         <v>Deportista</v>
@@ -2550,10 +2550,10 @@
         <v>Manual</v>
       </c>
       <c r="L49" t="str">
-        <v>8º CONTROL PROVINCIAL A+B+C+D (4-3)</v>
+        <v>Control Libre Infantil y 7ª Control Junior y Absoluto Valencia</v>
       </c>
       <c r="M49" t="str">
-        <v>SEDAVI</v>
+        <v>Sedavi</v>
       </c>
       <c r="N49" t="str">
         <v>No</v>
@@ -2561,28 +2561,28 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>1</v>
+        <v>49</v>
       </c>
       <c r="B50" t="str">
-        <v>100 Libre</v>
+        <v>50 Libre</v>
       </c>
       <c r="C50" t="str">
-        <v>MARIA VICENTE VILLAMON</v>
+        <v>ZULEMA VIDAL HERRERO</v>
       </c>
       <c r="D50">
-        <v>2008</v>
+        <v>1998</v>
       </c>
       <c r="E50" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F50" t="str">
-        <v>00:01:00.64</v>
+        <v>00:00:45.28</v>
       </c>
       <c r="G50">
-        <v>620</v>
+        <v>142</v>
       </c>
       <c r="H50" s="1">
-        <v>45683.99949074074</v>
+        <v>42539.99949074074</v>
       </c>
       <c r="I50" t="str">
         <v>Deportista</v>
@@ -2591,13 +2591,13 @@
         <v>50m</v>
       </c>
       <c r="K50" t="str">
-        <v>Electrónico</v>
+        <v>Manual</v>
       </c>
       <c r="L50" t="str">
-        <v>XXX MEMORIAL PASCUAL ROMAN</v>
+        <v>8º CONTROL PROVINCIAL A+B+C+D (4-3)</v>
       </c>
       <c r="M50" t="str">
-        <v>Elche</v>
+        <v>SEDAVI</v>
       </c>
       <c r="N50" t="str">
         <v>No</v>
@@ -2605,28 +2605,28 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B51" t="str">
         <v>100 Libre</v>
       </c>
       <c r="C51" t="str">
-        <v>IRENE JIMENEZ PEREZ</v>
+        <v>MARIA VICENTE VILLAMON</v>
       </c>
       <c r="D51">
-        <v>1992</v>
+        <v>2008</v>
       </c>
       <c r="E51" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F51" t="str">
-        <v>00:01:01.23</v>
+        <v>00:01:00.64</v>
       </c>
       <c r="G51">
-        <v>602</v>
+        <v>620</v>
       </c>
       <c r="H51" s="1">
-        <v>44745.99949074074</v>
+        <v>45683.99949074074</v>
       </c>
       <c r="I51" t="str">
         <v>Deportista</v>
@@ -2638,10 +2638,10 @@
         <v>Electrónico</v>
       </c>
       <c r="L51" t="str">
-        <v>Campeonato Autonómico Jr y Abs de Verano OPEN P50</v>
+        <v>XXX MEMORIAL PASCUAL ROMAN</v>
       </c>
       <c r="M51" t="str">
-        <v>Castellón</v>
+        <v>Elche</v>
       </c>
       <c r="N51" t="str">
         <v>No</v>
@@ -2649,28 +2649,28 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B52" t="str">
         <v>100 Libre</v>
       </c>
       <c r="C52" t="str">
-        <v>ANGELS REQUENA MARTINEZ</v>
+        <v>IRENE JIMENEZ PEREZ</v>
       </c>
       <c r="D52">
-        <v>2012</v>
+        <v>1992</v>
       </c>
       <c r="E52" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F52" t="str">
-        <v>00:01:03.37</v>
+        <v>00:01:01.23</v>
       </c>
       <c r="G52">
-        <v>543</v>
+        <v>602</v>
       </c>
       <c r="H52" s="1">
-        <v>46047.99949074074</v>
+        <v>44745.99949074074</v>
       </c>
       <c r="I52" t="str">
         <v>Deportista</v>
@@ -2682,10 +2682,10 @@
         <v>Electrónico</v>
       </c>
       <c r="L52" t="str">
-        <v>TROFEO INTERNACIONAL XXXI MEMORIAL PASCUAL ROMAN</v>
+        <v>Campeonato Autonómico Jr y Abs de Verano OPEN P50</v>
       </c>
       <c r="M52" t="str">
-        <v>Elche</v>
+        <v>Castellón</v>
       </c>
       <c r="N52" t="str">
         <v>No</v>
@@ -2693,28 +2693,28 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B53" t="str">
         <v>100 Libre</v>
       </c>
       <c r="C53" t="str">
-        <v>INES PEDRERO MARTINEZ</v>
+        <v>ANGELS REQUENA MARTINEZ</v>
       </c>
       <c r="D53">
-        <v>2008</v>
+        <v>2012</v>
       </c>
       <c r="E53" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F53" t="str">
-        <v>00:01:03.76</v>
+        <v>00:01:03.37</v>
       </c>
       <c r="G53">
-        <v>533</v>
+        <v>543</v>
       </c>
       <c r="H53" s="1">
-        <v>45802.99949074074</v>
+        <v>46047.99949074074</v>
       </c>
       <c r="I53" t="str">
         <v>Deportista</v>
@@ -2726,10 +2726,10 @@
         <v>Electrónico</v>
       </c>
       <c r="L53" t="str">
-        <v>CAMPEONATO AUTONOMICO JUNIOR Y ABSOLUTO DE VERANO 2025</v>
+        <v>TROFEO INTERNACIONAL XXXI MEMORIAL PASCUAL ROMAN</v>
       </c>
       <c r="M53" t="str">
-        <v>Castellón</v>
+        <v>Elche</v>
       </c>
       <c r="N53" t="str">
         <v>No</v>
@@ -2737,28 +2737,28 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B54" t="str">
         <v>100 Libre</v>
       </c>
       <c r="C54" t="str">
-        <v>LUCIA ISABEL SANCHEZ CHECA</v>
+        <v>INES PEDRERO MARTINEZ</v>
       </c>
       <c r="D54">
-        <v>2003</v>
+        <v>2008</v>
       </c>
       <c r="E54" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F54" t="str">
-        <v>00:01:04.22</v>
+        <v>00:01:03.76</v>
       </c>
       <c r="G54">
-        <v>522</v>
+        <v>533</v>
       </c>
       <c r="H54" s="1">
-        <v>45696.99949074074</v>
+        <v>45802.99949074074</v>
       </c>
       <c r="I54" t="str">
         <v>Deportista</v>
@@ -2770,24 +2770,24 @@
         <v>Electrónico</v>
       </c>
       <c r="L54" t="str">
-        <v>CAMPEONATO AUTONOMICO JUNIOR Y ABSOLUTO DE INVIERNO 2025 C.V.</v>
+        <v>CAMPEONATO AUTONOMICO JUNIOR Y ABSOLUTO DE VERANO 2025</v>
       </c>
       <c r="M54" t="str">
         <v>Castellón</v>
       </c>
       <c r="N54" t="str">
-        <v>Sí</v>
+        <v>No</v>
       </c>
     </row>
     <row r="55">
       <c r="A55">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B55" t="str">
         <v>100 Libre</v>
       </c>
       <c r="C55" t="str">
-        <v>ALBA IZQUIERDO LOPEZ</v>
+        <v>LUCIA ISABEL SANCHEZ CHECA</v>
       </c>
       <c r="D55">
         <v>2003</v>
@@ -2796,13 +2796,13 @@
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F55" t="str">
-        <v>00:01:04.80</v>
+        <v>00:01:04.22</v>
       </c>
       <c r="G55">
-        <v>508</v>
+        <v>522</v>
       </c>
       <c r="H55" s="1">
-        <v>44745.99949074074</v>
+        <v>45696.99949074074</v>
       </c>
       <c r="I55" t="str">
         <v>Deportista</v>
@@ -2814,39 +2814,39 @@
         <v>Electrónico</v>
       </c>
       <c r="L55" t="str">
-        <v>Campeonato Autonómico Jr y Abs de Verano OPEN P50</v>
+        <v>CAMPEONATO AUTONOMICO JUNIOR Y ABSOLUTO DE INVIERNO 2025 C.V.</v>
       </c>
       <c r="M55" t="str">
         <v>Castellón</v>
       </c>
       <c r="N55" t="str">
-        <v>No</v>
+        <v>Sí</v>
       </c>
     </row>
     <row r="56">
       <c r="A56">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B56" t="str">
         <v>100 Libre</v>
       </c>
       <c r="C56" t="str">
-        <v>INES BERMEJO ALBERO</v>
+        <v>ALBA IZQUIERDO LOPEZ</v>
       </c>
       <c r="D56">
-        <v>1992</v>
+        <v>2003</v>
       </c>
       <c r="E56" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F56" t="str">
-        <v>00:01:04.81</v>
+        <v>00:01:04.80</v>
       </c>
       <c r="G56">
         <v>508</v>
       </c>
       <c r="H56" s="1">
-        <v>44367.99949074074</v>
+        <v>44745.99949074074</v>
       </c>
       <c r="I56" t="str">
         <v>Deportista</v>
@@ -2855,13 +2855,13 @@
         <v>50m</v>
       </c>
       <c r="K56" t="str">
-        <v>Manual</v>
+        <v>Electrónico</v>
       </c>
       <c r="L56" t="str">
-        <v>PRUEBAS DE ACCESO AUTONÓMICO INFANTIL Y MAYORES 3 CASTELLON</v>
+        <v>Campeonato Autonómico Jr y Abs de Verano OPEN P50</v>
       </c>
       <c r="M56" t="str">
-        <v>CASTELLON</v>
+        <v>Castellón</v>
       </c>
       <c r="N56" t="str">
         <v>No</v>
@@ -2869,28 +2869,28 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B57" t="str">
         <v>100 Libre</v>
       </c>
       <c r="C57" t="str">
-        <v>SARA MESA BELTRAN</v>
+        <v>INES BERMEJO ALBERO</v>
       </c>
       <c r="D57">
-        <v>2010</v>
+        <v>1992</v>
       </c>
       <c r="E57" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F57" t="str">
-        <v>00:01:05.13</v>
+        <v>00:01:04.81</v>
       </c>
       <c r="G57">
-        <v>500</v>
+        <v>508</v>
       </c>
       <c r="H57" s="1">
-        <v>46144.99949074074</v>
+        <v>44367.99949074074</v>
       </c>
       <c r="I57" t="str">
         <v>Deportista</v>
@@ -2899,13 +2899,13 @@
         <v>50m</v>
       </c>
       <c r="K57" t="str">
-        <v>Electrónico</v>
+        <v>Manual</v>
       </c>
       <c r="L57" t="str">
-        <v>XX TROFEO INTERNACIONAL IBERCAJA CIUDAD ZARAGOZA 2026 XVII MEMORIAL EDUARDO LASTRADA</v>
+        <v>PRUEBAS DE ACCESO AUTONÓMICO INFANTIL Y MAYORES 3 CASTELLON</v>
       </c>
       <c r="M57" t="str">
-        <v>ZARAGOZA (C)</v>
+        <v>CASTELLON</v>
       </c>
       <c r="N57" t="str">
         <v>No</v>
@@ -2913,7 +2913,7 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B58" t="str">
         <v>100 Libre</v>
@@ -2928,13 +2928,13 @@
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F58" t="str">
-        <v>00:01:05.22</v>
+        <v>00:01:05.03</v>
       </c>
       <c r="G58">
-        <v>498</v>
+        <v>503</v>
       </c>
       <c r="H58" s="1">
-        <v>46144.99949074074</v>
+        <v>46200.99949074074</v>
       </c>
       <c r="I58" t="str">
         <v>Deportista</v>
@@ -2946,10 +2946,10 @@
         <v>Electrónico</v>
       </c>
       <c r="L58" t="str">
-        <v>XX TROFEO INTERNACIONAL IBERCAJA CIUDAD ZARAGOZA 2026 XVII MEMORIAL EDUARDO LASTRADA</v>
+        <v>CAMPEONATO AUTONOMICO INFANTIL DE VERANO DE LA C.V. 2026</v>
       </c>
       <c r="M58" t="str">
-        <v>ZARAGOZA (C)</v>
+        <v>CASTELLON</v>
       </c>
       <c r="N58" t="str">
         <v>No</v>
@@ -2957,28 +2957,28 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B59" t="str">
         <v>100 Libre</v>
       </c>
       <c r="C59" t="str">
-        <v>SOFIA CALABUIG MARTINEZ</v>
+        <v>SARA MESA BELTRAN</v>
       </c>
       <c r="D59">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="E59" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F59" t="str">
-        <v>00:01:05.44</v>
+        <v>00:01:05.13</v>
       </c>
       <c r="G59">
-        <v>493</v>
+        <v>500</v>
       </c>
       <c r="H59" s="1">
-        <v>46081.99949074074</v>
+        <v>46144.99949074074</v>
       </c>
       <c r="I59" t="str">
         <v>Deportista</v>
@@ -2990,10 +2990,10 @@
         <v>Electrónico</v>
       </c>
       <c r="L59" t="str">
-        <v>CAMPEONATO AUTONOMICO INFANTIL DE INVIERNO 2026</v>
+        <v>XX TROFEO INTERNACIONAL IBERCAJA CIUDAD ZARAGOZA 2026 XVII MEMORIAL EDUARDO LASTRADA</v>
       </c>
       <c r="M59" t="str">
-        <v>CASTELLÓN</v>
+        <v>ZARAGOZA (C)</v>
       </c>
       <c r="N59" t="str">
         <v>No</v>
@@ -3001,28 +3001,28 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B60" t="str">
         <v>100 Libre</v>
       </c>
       <c r="C60" t="str">
-        <v>LUCIA CUEVAS CASAS</v>
+        <v>MARIA ANGELES GRASSO CUENCA</v>
       </c>
       <c r="D60">
-        <v>2006</v>
+        <v>2011</v>
       </c>
       <c r="E60" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F60" t="str">
-        <v>00:01:05.67</v>
+        <v>00:01:05.19</v>
       </c>
       <c r="G60">
-        <v>488</v>
+        <v>499</v>
       </c>
       <c r="H60" s="1">
-        <v>45116.99949074074</v>
+        <v>46200.99949074074</v>
       </c>
       <c r="I60" t="str">
         <v>Deportista</v>
@@ -3034,10 +3034,10 @@
         <v>Electrónico</v>
       </c>
       <c r="L60" t="str">
-        <v>CAMPEONATO AUTONÓMICO JUNIOR Y ABSOLUTO DE VERANO 2023</v>
+        <v>CAMPEONATO AUTONOMICO INFANTIL DE VERANO DE LA C.V. 2026</v>
       </c>
       <c r="M60" t="str">
-        <v>Castellón</v>
+        <v>CASTELLON</v>
       </c>
       <c r="N60" t="str">
         <v>No</v>
@@ -3045,28 +3045,28 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B61" t="str">
         <v>100 Libre</v>
       </c>
       <c r="C61" t="str">
-        <v>ANA MORALES ORTOLA</v>
+        <v>SOFIA CALABUIG MARTINEZ</v>
       </c>
       <c r="D61">
-        <v>2002</v>
+        <v>2011</v>
       </c>
       <c r="E61" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F61" t="str">
-        <v>00:01:05.81</v>
+        <v>00:01:05.44</v>
       </c>
       <c r="G61">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="H61" s="1">
-        <v>44989.99949074074</v>
+        <v>46081.99949074074</v>
       </c>
       <c r="I61" t="str">
         <v>Deportista</v>
@@ -3078,10 +3078,10 @@
         <v>Electrónico</v>
       </c>
       <c r="L61" t="str">
-        <v>CAMPEONATO AUTONÓMICO JUNIOR Y ABSOLUTO DE INVIERNO 2023</v>
+        <v>CAMPEONATO AUTONOMICO INFANTIL DE INVIERNO 2026</v>
       </c>
       <c r="M61" t="str">
-        <v>Elche</v>
+        <v>CASTELLÓN</v>
       </c>
       <c r="N61" t="str">
         <v>No</v>
@@ -3089,28 +3089,28 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B62" t="str">
         <v>100 Libre</v>
       </c>
       <c r="C62" t="str">
-        <v>JUDITH HERGUETA VICIANO</v>
+        <v>LUCIA CUEVAS CASAS</v>
       </c>
       <c r="D62">
-        <v>2008</v>
+        <v>2006</v>
       </c>
       <c r="E62" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F62" t="str">
-        <v>00:01:06.36</v>
+        <v>00:01:05.67</v>
       </c>
       <c r="G62">
-        <v>473</v>
+        <v>488</v>
       </c>
       <c r="H62" s="1">
-        <v>45801.99949074074</v>
+        <v>45116.99949074074</v>
       </c>
       <c r="I62" t="str">
         <v>Deportista</v>
@@ -3122,39 +3122,39 @@
         <v>Electrónico</v>
       </c>
       <c r="L62" t="str">
-        <v>CAMPEONATO AUTONOMICO JUNIOR Y ABSOLUTO DE VERANO 2025</v>
+        <v>CAMPEONATO AUTONÓMICO JUNIOR Y ABSOLUTO DE VERANO 2023</v>
       </c>
       <c r="M62" t="str">
         <v>Castellón</v>
       </c>
       <c r="N62" t="str">
-        <v>Sí</v>
+        <v>No</v>
       </c>
     </row>
     <row r="63">
       <c r="A63">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B63" t="str">
         <v>100 Libre</v>
       </c>
       <c r="C63" t="str">
-        <v>SOFIA VICTORIA ESTACIO ROMAN</v>
+        <v>ANA MORALES ORTOLA</v>
       </c>
       <c r="D63">
-        <v>2008</v>
+        <v>2002</v>
       </c>
       <c r="E63" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F63" t="str">
-        <v>00:01:06.69</v>
+        <v>00:01:05.81</v>
       </c>
       <c r="G63">
-        <v>466</v>
+        <v>485</v>
       </c>
       <c r="H63" s="1">
-        <v>45683.99949074074</v>
+        <v>44989.99949074074</v>
       </c>
       <c r="I63" t="str">
         <v>Deportista</v>
@@ -3166,7 +3166,7 @@
         <v>Electrónico</v>
       </c>
       <c r="L63" t="str">
-        <v>XXX MEMORIAL PASCUAL ROMAN</v>
+        <v>CAMPEONATO AUTONÓMICO JUNIOR Y ABSOLUTO DE INVIERNO 2023</v>
       </c>
       <c r="M63" t="str">
         <v>Elche</v>
@@ -3177,28 +3177,28 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B64" t="str">
         <v>100 Libre</v>
       </c>
       <c r="C64" t="str">
-        <v>ISABEL MORAGUES GINER</v>
+        <v>JUDITH HERGUETA VICIANO</v>
       </c>
       <c r="D64">
-        <v>2005</v>
+        <v>2008</v>
       </c>
       <c r="E64" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F64" t="str">
-        <v>00:01:07.35</v>
+        <v>00:01:06.36</v>
       </c>
       <c r="G64">
-        <v>453</v>
+        <v>473</v>
       </c>
       <c r="H64" s="1">
-        <v>45683.99949074074</v>
+        <v>45801.99949074074</v>
       </c>
       <c r="I64" t="str">
         <v>Deportista</v>
@@ -3210,39 +3210,39 @@
         <v>Electrónico</v>
       </c>
       <c r="L64" t="str">
-        <v>XXX MEMORIAL PASCUAL ROMAN</v>
+        <v>CAMPEONATO AUTONOMICO JUNIOR Y ABSOLUTO DE VERANO 2025</v>
       </c>
       <c r="M64" t="str">
-        <v>Elche</v>
+        <v>Castellón</v>
       </c>
       <c r="N64" t="str">
-        <v>No</v>
+        <v>Sí</v>
       </c>
     </row>
     <row r="65">
       <c r="A65">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B65" t="str">
         <v>100 Libre</v>
       </c>
       <c r="C65" t="str">
-        <v>MARIA ANGELES GRASSO CUENCA</v>
+        <v>SOFIA VICTORIA ESTACIO ROMAN</v>
       </c>
       <c r="D65">
-        <v>2011</v>
+        <v>2008</v>
       </c>
       <c r="E65" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F65" t="str">
-        <v>00:01:07.80</v>
+        <v>00:01:06.69</v>
       </c>
       <c r="G65">
-        <v>444</v>
+        <v>466</v>
       </c>
       <c r="H65" s="1">
-        <v>46144.99949074074</v>
+        <v>45683.99949074074</v>
       </c>
       <c r="I65" t="str">
         <v>Deportista</v>
@@ -3254,10 +3254,10 @@
         <v>Electrónico</v>
       </c>
       <c r="L65" t="str">
-        <v>XX TROFEO INTERNACIONAL IBERCAJA CIUDAD ZARAGOZA 2026 XVII MEMORIAL EDUARDO LASTRADA</v>
+        <v>XXX MEMORIAL PASCUAL ROMAN</v>
       </c>
       <c r="M65" t="str">
-        <v>ZARAGOZA (C)</v>
+        <v>Elche</v>
       </c>
       <c r="N65" t="str">
         <v>No</v>
@@ -3265,28 +3265,28 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B66" t="str">
         <v>100 Libre</v>
       </c>
       <c r="C66" t="str">
-        <v>VEGA ALCANTARA SANTA CRUZ</v>
+        <v>ISABEL MORAGUES GINER</v>
       </c>
       <c r="D66">
-        <v>2011</v>
+        <v>2005</v>
       </c>
       <c r="E66" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F66" t="str">
-        <v>00:01:08.08</v>
+        <v>00:01:07.35</v>
       </c>
       <c r="G66">
-        <v>438</v>
+        <v>453</v>
       </c>
       <c r="H66" s="1">
-        <v>46081.99949074074</v>
+        <v>45683.99949074074</v>
       </c>
       <c r="I66" t="str">
         <v>Deportista</v>
@@ -3298,10 +3298,10 @@
         <v>Electrónico</v>
       </c>
       <c r="L66" t="str">
-        <v>CAMPEONATO AUTONOMICO INFANTIL DE INVIERNO 2026</v>
+        <v>XXX MEMORIAL PASCUAL ROMAN</v>
       </c>
       <c r="M66" t="str">
-        <v>CASTELLÓN</v>
+        <v>Elche</v>
       </c>
       <c r="N66" t="str">
         <v>No</v>
@@ -3309,28 +3309,28 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B67" t="str">
         <v>100 Libre</v>
       </c>
       <c r="C67" t="str">
-        <v>MANUELA RADEANU</v>
+        <v>VEGA ALCANTARA SANTA CRUZ</v>
       </c>
       <c r="D67">
-        <v>2007</v>
+        <v>2011</v>
       </c>
       <c r="E67" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F67" t="str">
-        <v>00:01:08.16</v>
+        <v>00:01:08.08</v>
       </c>
       <c r="G67">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="H67" s="1">
-        <v>44381.99949074074</v>
+        <v>46081.99949074074</v>
       </c>
       <c r="I67" t="str">
         <v>Deportista</v>
@@ -3342,10 +3342,10 @@
         <v>Electrónico</v>
       </c>
       <c r="L67" t="str">
-        <v>Autonomico Infantil Verano</v>
+        <v>CAMPEONATO AUTONOMICO INFANTIL DE INVIERNO 2026</v>
       </c>
       <c r="M67" t="str">
-        <v>Castellon</v>
+        <v>CASTELLÓN</v>
       </c>
       <c r="N67" t="str">
         <v>No</v>
@@ -3353,28 +3353,28 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B68" t="str">
         <v>100 Libre</v>
       </c>
       <c r="C68" t="str">
-        <v>ADRIANA DIAZ CUEVAS</v>
+        <v>MANUELA RADEANU</v>
       </c>
       <c r="D68">
-        <v>2010</v>
+        <v>2007</v>
       </c>
       <c r="E68" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F68" t="str">
-        <v>00:01:09.61</v>
+        <v>00:01:08.16</v>
       </c>
       <c r="G68">
-        <v>410</v>
+        <v>437</v>
       </c>
       <c r="H68" s="1">
-        <v>45710.99949074074</v>
+        <v>44381.99949074074</v>
       </c>
       <c r="I68" t="str">
         <v>Deportista</v>
@@ -3386,10 +3386,10 @@
         <v>Electrónico</v>
       </c>
       <c r="L68" t="str">
-        <v>CAMPEONATO AUTONOMICO INFANTIL DE INVIERNO 2025 C.V.</v>
+        <v>Autonomico Infantil Verano</v>
       </c>
       <c r="M68" t="str">
-        <v>ELCHE</v>
+        <v>Castellon</v>
       </c>
       <c r="N68" t="str">
         <v>No</v>
@@ -3397,28 +3397,28 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B69" t="str">
         <v>100 Libre</v>
       </c>
       <c r="C69" t="str">
-        <v>ARIADNA MANZANEDA GARCIA</v>
+        <v>ADRIANA DIAZ CUEVAS</v>
       </c>
       <c r="D69">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="E69" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F69" t="str">
-        <v>00:01:10.24</v>
+        <v>00:01:09.61</v>
       </c>
       <c r="G69">
-        <v>399</v>
+        <v>410</v>
       </c>
       <c r="H69" s="1">
-        <v>46173.99949074074</v>
+        <v>45710.99949074074</v>
       </c>
       <c r="I69" t="str">
         <v>Deportista</v>
@@ -3427,42 +3427,42 @@
         <v>50m</v>
       </c>
       <c r="K69" t="str">
-        <v>Manual</v>
+        <v>Electrónico</v>
       </c>
       <c r="L69" t="str">
-        <v>LVI TROFEU SANT PASCUAL XXXVII MEMORIAL JOSE VICENTE MARTI BARRACHINA</v>
+        <v>CAMPEONATO AUTONOMICO INFANTIL DE INVIERNO 2025 C.V.</v>
       </c>
       <c r="M69" t="str">
-        <v>Vila-Real</v>
+        <v>ELCHE</v>
       </c>
       <c r="N69" t="str">
-        <v>Sí</v>
+        <v>No</v>
       </c>
     </row>
     <row r="70">
       <c r="A70">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B70" t="str">
         <v>100 Libre</v>
       </c>
       <c r="C70" t="str">
-        <v>ROCIO MARTINEZ GONZALEZ</v>
+        <v>ARIADNA MANZANEDA GARCIA</v>
       </c>
       <c r="D70">
-        <v>2011</v>
+        <v>2012</v>
       </c>
       <c r="E70" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F70" t="str">
-        <v>00:01:10.31</v>
+        <v>00:01:10.24</v>
       </c>
       <c r="G70">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="H70" s="1">
-        <v>46081.99949074074</v>
+        <v>46173.99949074074</v>
       </c>
       <c r="I70" t="str">
         <v>Deportista</v>
@@ -3471,42 +3471,42 @@
         <v>50m</v>
       </c>
       <c r="K70" t="str">
-        <v>Electrónico</v>
+        <v>Manual</v>
       </c>
       <c r="L70" t="str">
-        <v>CAMPEONATO AUTONOMICO INFANTIL DE INVIERNO 2026</v>
+        <v>LVI TROFEU SANT PASCUAL XXXVII MEMORIAL JOSE VICENTE MARTI BARRACHINA</v>
       </c>
       <c r="M70" t="str">
-        <v>CASTELLÓN</v>
+        <v>Vila-Real</v>
       </c>
       <c r="N70" t="str">
-        <v>No</v>
+        <v>Sí</v>
       </c>
     </row>
     <row r="71">
       <c r="A71">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B71" t="str">
         <v>100 Libre</v>
       </c>
       <c r="C71" t="str">
-        <v>CAMILA GUEVARA PEROZO</v>
+        <v>ROCIO MARTINEZ GONZALEZ</v>
       </c>
       <c r="D71">
-        <v>2010</v>
+        <v>2011</v>
       </c>
       <c r="E71" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F71" t="str">
-        <v>00:01:10.78</v>
+        <v>00:01:10.31</v>
       </c>
       <c r="G71">
-        <v>390</v>
+        <v>398</v>
       </c>
       <c r="H71" s="1">
-        <v>45710.99949074074</v>
+        <v>46081.99949074074</v>
       </c>
       <c r="I71" t="str">
         <v>Deportista</v>
@@ -3518,10 +3518,10 @@
         <v>Electrónico</v>
       </c>
       <c r="L71" t="str">
-        <v>CAMPEONATO AUTONOMICO INFANTIL DE INVIERNO 2025 C.V.</v>
+        <v>CAMPEONATO AUTONOMICO INFANTIL DE INVIERNO 2026</v>
       </c>
       <c r="M71" t="str">
-        <v>ELCHE</v>
+        <v>CASTELLÓN</v>
       </c>
       <c r="N71" t="str">
         <v>No</v>
@@ -3529,13 +3529,13 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B72" t="str">
         <v>100 Libre</v>
       </c>
       <c r="C72" t="str">
-        <v>PAOLA MEIJIDE VILLANUEVA</v>
+        <v>CAMILA GUEVARA PEROZO</v>
       </c>
       <c r="D72">
         <v>2010</v>
@@ -3544,13 +3544,13 @@
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F72" t="str">
-        <v>00:01:11.43</v>
+        <v>00:01:10.78</v>
       </c>
       <c r="G72">
-        <v>379</v>
+        <v>390</v>
       </c>
       <c r="H72" s="1">
-        <v>45836.99949074074</v>
+        <v>45710.99949074074</v>
       </c>
       <c r="I72" t="str">
         <v>Deportista</v>
@@ -3562,10 +3562,10 @@
         <v>Electrónico</v>
       </c>
       <c r="L72" t="str">
-        <v>CAMPEONATO AUTONOMICO INFANTIL DE VERANO 2025</v>
+        <v>CAMPEONATO AUTONOMICO INFANTIL DE INVIERNO 2025 C.V.</v>
       </c>
       <c r="M72" t="str">
-        <v>Castellón</v>
+        <v>ELCHE</v>
       </c>
       <c r="N72" t="str">
         <v>No</v>
@@ -3573,28 +3573,28 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B73" t="str">
         <v>100 Libre</v>
       </c>
       <c r="C73" t="str">
-        <v>DARIA ILIYANOVA KIRYAKOVA</v>
+        <v>PAOLA MEIJIDE VILLANUEVA</v>
       </c>
       <c r="D73">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="E73" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F73" t="str">
-        <v>00:01:11.54</v>
+        <v>00:01:11.43</v>
       </c>
       <c r="G73">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="H73" s="1">
-        <v>46173.99949074074</v>
+        <v>45836.99949074074</v>
       </c>
       <c r="I73" t="str">
         <v>Deportista</v>
@@ -3603,13 +3603,13 @@
         <v>50m</v>
       </c>
       <c r="K73" t="str">
-        <v>Manual</v>
+        <v>Electrónico</v>
       </c>
       <c r="L73" t="str">
-        <v>LVI TROFEU SANT PASCUAL XXXVII MEMORIAL JOSE VICENTE MARTI BARRACHINA</v>
+        <v>CAMPEONATO AUTONOMICO INFANTIL DE VERANO 2025</v>
       </c>
       <c r="M73" t="str">
-        <v>Vila-Real</v>
+        <v>Castellón</v>
       </c>
       <c r="N73" t="str">
         <v>No</v>
@@ -3617,28 +3617,28 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B74" t="str">
         <v>100 Libre</v>
       </c>
       <c r="C74" t="str">
-        <v>EVA CALABUIG TRIGO</v>
+        <v>DARIA ILIYANOVA KIRYAKOVA</v>
       </c>
       <c r="D74">
-        <v>2000</v>
+        <v>2012</v>
       </c>
       <c r="E74" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F74" t="str">
-        <v>00:01:12.07</v>
+        <v>00:01:11.54</v>
       </c>
       <c r="G74">
-        <v>369</v>
+        <v>378</v>
       </c>
       <c r="H74" s="1">
-        <v>43638.99949074074</v>
+        <v>46173.99949074074</v>
       </c>
       <c r="I74" t="str">
         <v>Deportista</v>
@@ -3650,10 +3650,10 @@
         <v>Manual</v>
       </c>
       <c r="L74" t="str">
-        <v>7ª Jornada Control infa y mayores</v>
+        <v>LVI TROFEU SANT PASCUAL XXXVII MEMORIAL JOSE VICENTE MARTI BARRACHINA</v>
       </c>
       <c r="M74" t="str">
-        <v>Moncada</v>
+        <v>Vila-Real</v>
       </c>
       <c r="N74" t="str">
         <v>No</v>
@@ -3661,13 +3661,13 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B75" t="str">
         <v>100 Libre</v>
       </c>
       <c r="C75" t="str">
-        <v>CELIA PARDO BARRIO</v>
+        <v>EVA CALABUIG TRIGO</v>
       </c>
       <c r="D75">
         <v>2000</v>
@@ -3676,13 +3676,13 @@
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F75" t="str">
-        <v>00:01:13.16</v>
+        <v>00:01:12.07</v>
       </c>
       <c r="G75">
-        <v>353</v>
+        <v>369</v>
       </c>
       <c r="H75" s="1">
-        <v>42903.99949074074</v>
+        <v>43638.99949074074</v>
       </c>
       <c r="I75" t="str">
         <v>Deportista</v>
@@ -3691,13 +3691,13 @@
         <v>50m</v>
       </c>
       <c r="K75" t="str">
-        <v>Electrónico</v>
+        <v>Manual</v>
       </c>
       <c r="L75" t="str">
-        <v>VI TROFEO REAL CLUB NATACION DELFIN</v>
+        <v>7ª Jornada Control infa y mayores</v>
       </c>
       <c r="M75" t="str">
-        <v>PARQUE OESTE</v>
+        <v>Moncada</v>
       </c>
       <c r="N75" t="str">
         <v>No</v>
@@ -3705,28 +3705,28 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B76" t="str">
         <v>100 Libre</v>
       </c>
       <c r="C76" t="str">
-        <v>MARIA MENDOZA GOMEZ</v>
+        <v>CELIA PARDO BARRIO</v>
       </c>
       <c r="D76">
-        <v>2003</v>
+        <v>2000</v>
       </c>
       <c r="E76" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F76" t="str">
-        <v>00:01:13.18</v>
+        <v>00:01:13.16</v>
       </c>
       <c r="G76">
         <v>353</v>
       </c>
       <c r="H76" s="1">
-        <v>43638.99949074074</v>
+        <v>42903.99949074074</v>
       </c>
       <c r="I76" t="str">
         <v>Deportista</v>
@@ -3735,13 +3735,13 @@
         <v>50m</v>
       </c>
       <c r="K76" t="str">
-        <v>Manual</v>
+        <v>Electrónico</v>
       </c>
       <c r="L76" t="str">
-        <v>7ª Jornada Control infa y mayores</v>
+        <v>VI TROFEO REAL CLUB NATACION DELFIN</v>
       </c>
       <c r="M76" t="str">
-        <v>Moncada</v>
+        <v>PARQUE OESTE</v>
       </c>
       <c r="N76" t="str">
         <v>No</v>
@@ -3749,25 +3749,25 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B77" t="str">
         <v>100 Libre</v>
       </c>
       <c r="C77" t="str">
-        <v>LAURA VILA ALZAMORA</v>
+        <v>MARIA MENDOZA GOMEZ</v>
       </c>
       <c r="D77">
-        <v>2005</v>
+        <v>2003</v>
       </c>
       <c r="E77" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F77" t="str">
-        <v>00:01:13.89</v>
+        <v>00:01:13.18</v>
       </c>
       <c r="G77">
-        <v>343</v>
+        <v>353</v>
       </c>
       <c r="H77" s="1">
         <v>43638.99949074074</v>
@@ -3793,28 +3793,28 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B78" t="str">
         <v>100 Libre</v>
       </c>
       <c r="C78" t="str">
-        <v>IRENE TAMARIT MUNERA</v>
+        <v>LAURA VILA ALZAMORA</v>
       </c>
       <c r="D78">
-        <v>2008</v>
+        <v>2005</v>
       </c>
       <c r="E78" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F78" t="str">
-        <v>00:01:14.04</v>
+        <v>00:01:13.89</v>
       </c>
       <c r="G78">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="H78" s="1">
-        <v>45108.99949074074</v>
+        <v>43638.99949074074</v>
       </c>
       <c r="I78" t="str">
         <v>Deportista</v>
@@ -3823,13 +3823,13 @@
         <v>50m</v>
       </c>
       <c r="K78" t="str">
-        <v>Electrónico</v>
+        <v>Manual</v>
       </c>
       <c r="L78" t="str">
-        <v>Campeonato Autonomico Infantil de Verano</v>
+        <v>7ª Jornada Control infa y mayores</v>
       </c>
       <c r="M78" t="str">
-        <v>ELDA</v>
+        <v>Moncada</v>
       </c>
       <c r="N78" t="str">
         <v>No</v>
@@ -3837,28 +3837,28 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B79" t="str">
         <v>100 Libre</v>
       </c>
       <c r="C79" t="str">
-        <v>DARIS IVANOVA STOYANOVA</v>
+        <v>IRENE TAMARIT MUNERA</v>
       </c>
       <c r="D79">
-        <v>2011</v>
+        <v>2008</v>
       </c>
       <c r="E79" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F79" t="str">
-        <v>00:01:14.93</v>
+        <v>00:01:14.04</v>
       </c>
       <c r="G79">
-        <v>329</v>
+        <v>341</v>
       </c>
       <c r="H79" s="1">
-        <v>45816.99949074074</v>
+        <v>45108.99949074074</v>
       </c>
       <c r="I79" t="str">
         <v>Deportista</v>
@@ -3870,10 +3870,10 @@
         <v>Electrónico</v>
       </c>
       <c r="L79" t="str">
-        <v>XIII TROFEO REAL CLUB NATACION DELFIN</v>
+        <v>Campeonato Autonomico Infantil de Verano</v>
       </c>
       <c r="M79" t="str">
-        <v>Castellón</v>
+        <v>ELDA</v>
       </c>
       <c r="N79" t="str">
         <v>No</v>
@@ -3881,28 +3881,28 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B80" t="str">
         <v>100 Libre</v>
       </c>
       <c r="C80" t="str">
-        <v>IRENE BELLVER OJEDA</v>
+        <v>LOLA FERRI BELLVER</v>
       </c>
       <c r="D80">
-        <v>2009</v>
+        <v>2012</v>
       </c>
       <c r="E80" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F80" t="str">
-        <v>00:01:14.94</v>
+        <v>00:01:14.25</v>
       </c>
       <c r="G80">
-        <v>329</v>
+        <v>338</v>
       </c>
       <c r="H80" s="1">
-        <v>45472.99949074074</v>
+        <v>46200.99949074074</v>
       </c>
       <c r="I80" t="str">
         <v>Deportista</v>
@@ -3914,39 +3914,39 @@
         <v>Electrónico</v>
       </c>
       <c r="L80" t="str">
-        <v>Autonomico Infantil de Verano</v>
+        <v>CAMPEONATO AUTONOMICO INFANTIL DE VERANO DE LA C.V. 2026</v>
       </c>
       <c r="M80" t="str">
-        <v>Sedavi(Valencia)</v>
+        <v>CASTELLON</v>
       </c>
       <c r="N80" t="str">
-        <v>No</v>
+        <v>Sí</v>
       </c>
     </row>
     <row r="81">
       <c r="A81">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B81" t="str">
         <v>100 Libre</v>
       </c>
       <c r="C81" t="str">
-        <v>MARTINA GOMEZ GONZALEZ</v>
+        <v>DARIS IVANOVA STOYANOVA</v>
       </c>
       <c r="D81">
-        <v>2007</v>
+        <v>2011</v>
       </c>
       <c r="E81" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F81" t="str">
-        <v>00:01:15.90</v>
+        <v>00:01:14.93</v>
       </c>
       <c r="G81">
-        <v>316</v>
+        <v>329</v>
       </c>
       <c r="H81" s="1">
-        <v>45095.99949074074</v>
+        <v>45816.99949074074</v>
       </c>
       <c r="I81" t="str">
         <v>Deportista</v>
@@ -3958,7 +3958,7 @@
         <v>Electrónico</v>
       </c>
       <c r="L81" t="str">
-        <v>I Trofeo Federación 226ERS piscina 50m</v>
+        <v>XIII TROFEO REAL CLUB NATACION DELFIN</v>
       </c>
       <c r="M81" t="str">
         <v>Castellón</v>
@@ -3969,28 +3969,28 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B82" t="str">
         <v>100 Libre</v>
       </c>
       <c r="C82" t="str">
-        <v>ALICIA FERNANDEZ CARO</v>
+        <v>IRENE BELLVER OJEDA</v>
       </c>
       <c r="D82">
-        <v>2012</v>
+        <v>2009</v>
       </c>
       <c r="E82" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F82" t="str">
-        <v>00:01:17.02</v>
+        <v>00:01:14.94</v>
       </c>
       <c r="G82">
-        <v>303</v>
+        <v>329</v>
       </c>
       <c r="H82" s="1">
-        <v>46173.99949074074</v>
+        <v>45472.99949074074</v>
       </c>
       <c r="I82" t="str">
         <v>Deportista</v>
@@ -3999,13 +3999,13 @@
         <v>50m</v>
       </c>
       <c r="K82" t="str">
-        <v>Manual</v>
+        <v>Electrónico</v>
       </c>
       <c r="L82" t="str">
-        <v>LVI TROFEU SANT PASCUAL XXXVII MEMORIAL JOSE VICENTE MARTI BARRACHINA</v>
+        <v>Autonomico Infantil de Verano</v>
       </c>
       <c r="M82" t="str">
-        <v>Vila-Real</v>
+        <v>Sedavi(Valencia)</v>
       </c>
       <c r="N82" t="str">
         <v>No</v>
@@ -4013,28 +4013,28 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B83" t="str">
         <v>100 Libre</v>
       </c>
       <c r="C83" t="str">
-        <v>BLANCA OCHOA ARENAS</v>
+        <v>MARTINA GOMEZ GONZALEZ</v>
       </c>
       <c r="D83">
-        <v>2000</v>
+        <v>2007</v>
       </c>
       <c r="E83" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F83" t="str">
-        <v>00:01:17.51</v>
+        <v>00:01:15.90</v>
       </c>
       <c r="G83">
-        <v>297</v>
+        <v>316</v>
       </c>
       <c r="H83" s="1">
-        <v>42707.99949074074</v>
+        <v>45095.99949074074</v>
       </c>
       <c r="I83" t="str">
         <v>Deportista</v>
@@ -4046,10 +4046,10 @@
         <v>Electrónico</v>
       </c>
       <c r="L83" t="str">
-        <v>TROFEO CASTALIA</v>
+        <v>I Trofeo Federación 226ERS piscina 50m</v>
       </c>
       <c r="M83" t="str">
-        <v>CASTELLÓN</v>
+        <v>Castellón</v>
       </c>
       <c r="N83" t="str">
         <v>No</v>
@@ -4057,28 +4057,28 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B84" t="str">
         <v>100 Libre</v>
       </c>
       <c r="C84" t="str">
-        <v>VERONICA MARIA GONZALEZ RUIZ</v>
+        <v>ALICIA FERNANDEZ CARO</v>
       </c>
       <c r="D84">
-        <v>2006</v>
+        <v>2012</v>
       </c>
       <c r="E84" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F84" t="str">
-        <v>00:01:17.57</v>
+        <v>00:01:17.02</v>
       </c>
       <c r="G84">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c r="H84" s="1">
-        <v>44709.99949074074</v>
+        <v>46173.99949074074</v>
       </c>
       <c r="I84" t="str">
         <v>Deportista</v>
@@ -4090,10 +4090,10 @@
         <v>Manual</v>
       </c>
       <c r="L84" t="str">
-        <v>Control Libre Infantil y 7ª Control Junior y Absoluto Valencia</v>
+        <v>LVI TROFEU SANT PASCUAL XXXVII MEMORIAL JOSE VICENTE MARTI BARRACHINA</v>
       </c>
       <c r="M84" t="str">
-        <v>Sedavi</v>
+        <v>Vila-Real</v>
       </c>
       <c r="N84" t="str">
         <v>No</v>
@@ -4101,13 +4101,13 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B85" t="str">
         <v>100 Libre</v>
       </c>
       <c r="C85" t="str">
-        <v>ALESSIA PAFUNDI</v>
+        <v>BLANCA OCHOA ARENAS</v>
       </c>
       <c r="D85">
         <v>2000</v>
@@ -4116,10 +4116,10 @@
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F85" t="str">
-        <v>00:01:19.58</v>
+        <v>00:01:17.51</v>
       </c>
       <c r="G85">
-        <v>274</v>
+        <v>297</v>
       </c>
       <c r="H85" s="1">
         <v>42707.99949074074</v>
@@ -4145,28 +4145,28 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B86" t="str">
         <v>100 Libre</v>
       </c>
       <c r="C86" t="str">
-        <v>VEGA HEREDIA SALGUERO</v>
+        <v>VERONICA MARIA GONZALEZ RUIZ</v>
       </c>
       <c r="D86">
-        <v>2012</v>
+        <v>2006</v>
       </c>
       <c r="E86" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F86" t="str">
-        <v>00:01:20.17</v>
+        <v>00:01:17.57</v>
       </c>
       <c r="G86">
-        <v>268</v>
+        <v>296</v>
       </c>
       <c r="H86" s="1">
-        <v>46173.99949074074</v>
+        <v>44709.99949074074</v>
       </c>
       <c r="I86" t="str">
         <v>Deportista</v>
@@ -4178,10 +4178,10 @@
         <v>Manual</v>
       </c>
       <c r="L86" t="str">
-        <v>LVI TROFEU SANT PASCUAL XXXVII MEMORIAL JOSE VICENTE MARTI BARRACHINA</v>
+        <v>Control Libre Infantil y 7ª Control Junior y Absoluto Valencia</v>
       </c>
       <c r="M86" t="str">
-        <v>Vila-Real</v>
+        <v>Sedavi</v>
       </c>
       <c r="N86" t="str">
         <v>No</v>
@@ -4189,28 +4189,28 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B87" t="str">
         <v>100 Libre</v>
       </c>
       <c r="C87" t="str">
-        <v>SOFIA PALOMEQUE RODRIGO</v>
+        <v>ALESSIA PAFUNDI</v>
       </c>
       <c r="D87">
-        <v>2008</v>
+        <v>2000</v>
       </c>
       <c r="E87" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F87" t="str">
-        <v>00:01:20.90</v>
+        <v>00:01:19.58</v>
       </c>
       <c r="G87">
-        <v>261</v>
+        <v>274</v>
       </c>
       <c r="H87" s="1">
-        <v>44709.99949074074</v>
+        <v>42707.99949074074</v>
       </c>
       <c r="I87" t="str">
         <v>Deportista</v>
@@ -4219,13 +4219,13 @@
         <v>50m</v>
       </c>
       <c r="K87" t="str">
-        <v>Manual</v>
+        <v>Electrónico</v>
       </c>
       <c r="L87" t="str">
-        <v>Control Libre Infantil y 7ª Control Junior y Absoluto Valencia</v>
+        <v>TROFEO CASTALIA</v>
       </c>
       <c r="M87" t="str">
-        <v>Sedavi</v>
+        <v>CASTELLÓN</v>
       </c>
       <c r="N87" t="str">
         <v>No</v>
@@ -4233,28 +4233,28 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B88" t="str">
         <v>100 Libre</v>
       </c>
       <c r="C88" t="str">
-        <v>INGRID MONTALVA TERCERO</v>
+        <v>VEGA HEREDIA SALGUERO</v>
       </c>
       <c r="D88">
-        <v>2008</v>
+        <v>2012</v>
       </c>
       <c r="E88" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F88" t="str">
-        <v>00:01:21.99</v>
+        <v>00:01:20.17</v>
       </c>
       <c r="G88">
-        <v>251</v>
+        <v>268</v>
       </c>
       <c r="H88" s="1">
-        <v>44709.99949074074</v>
+        <v>46173.99949074074</v>
       </c>
       <c r="I88" t="str">
         <v>Deportista</v>
@@ -4266,10 +4266,10 @@
         <v>Manual</v>
       </c>
       <c r="L88" t="str">
-        <v>Control Libre Infantil y 7ª Control Junior y Absoluto Valencia</v>
+        <v>LVI TROFEU SANT PASCUAL XXXVII MEMORIAL JOSE VICENTE MARTI BARRACHINA</v>
       </c>
       <c r="M88" t="str">
-        <v>Sedavi</v>
+        <v>Vila-Real</v>
       </c>
       <c r="N88" t="str">
         <v>No</v>
@@ -4277,28 +4277,28 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B89" t="str">
         <v>100 Libre</v>
       </c>
       <c r="C89" t="str">
-        <v>ALISA REBROVA</v>
+        <v>SOFIA PALOMEQUE RODRIGO</v>
       </c>
       <c r="D89">
-        <v>2012</v>
+        <v>2008</v>
       </c>
       <c r="E89" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F89" t="str">
-        <v>00:01:22.17</v>
+        <v>00:01:20.90</v>
       </c>
       <c r="G89">
-        <v>249</v>
+        <v>261</v>
       </c>
       <c r="H89" s="1">
-        <v>46173.99949074074</v>
+        <v>44709.99949074074</v>
       </c>
       <c r="I89" t="str">
         <v>Deportista</v>
@@ -4310,10 +4310,10 @@
         <v>Manual</v>
       </c>
       <c r="L89" t="str">
-        <v>LVI TROFEU SANT PASCUAL XXXVII MEMORIAL JOSE VICENTE MARTI BARRACHINA</v>
+        <v>Control Libre Infantil y 7ª Control Junior y Absoluto Valencia</v>
       </c>
       <c r="M89" t="str">
-        <v>Vila-Real</v>
+        <v>Sedavi</v>
       </c>
       <c r="N89" t="str">
         <v>No</v>
@@ -4321,25 +4321,25 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B90" t="str">
         <v>100 Libre</v>
       </c>
       <c r="C90" t="str">
-        <v>SANDRA DOMINGUEZ VALERO</v>
+        <v>INGRID MONTALVA TERCERO</v>
       </c>
       <c r="D90">
-        <v>2007</v>
+        <v>2008</v>
       </c>
       <c r="E90" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F90" t="str">
-        <v>00:01:22.38</v>
+        <v>00:01:21.99</v>
       </c>
       <c r="G90">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="H90" s="1">
         <v>44709.99949074074</v>
@@ -4365,28 +4365,28 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B91" t="str">
         <v>100 Libre</v>
       </c>
       <c r="C91" t="str">
-        <v>CLAUDIA LATORRE MARTIN</v>
+        <v>ALISA REBROVA</v>
       </c>
       <c r="D91">
-        <v>2009</v>
+        <v>2012</v>
       </c>
       <c r="E91" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F91" t="str">
-        <v>00:01:25.53</v>
+        <v>00:01:22.17</v>
       </c>
       <c r="G91">
-        <v>221</v>
+        <v>249</v>
       </c>
       <c r="H91" s="1">
-        <v>44709.99949074074</v>
+        <v>46173.99949074074</v>
       </c>
       <c r="I91" t="str">
         <v>Deportista</v>
@@ -4398,10 +4398,10 @@
         <v>Manual</v>
       </c>
       <c r="L91" t="str">
-        <v>Control Libre Infantil y 7ª Control Junior y Absoluto Valencia</v>
+        <v>LVI TROFEU SANT PASCUAL XXXVII MEMORIAL JOSE VICENTE MARTI BARRACHINA</v>
       </c>
       <c r="M91" t="str">
-        <v>Sedavi</v>
+        <v>Vila-Real</v>
       </c>
       <c r="N91" t="str">
         <v>No</v>
@@ -4409,13 +4409,13 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B92" t="str">
         <v>100 Libre</v>
       </c>
       <c r="C92" t="str">
-        <v>VALERIA RUIZ ORTIZ</v>
+        <v>SANDRA DOMINGUEZ VALERO</v>
       </c>
       <c r="D92">
         <v>2007</v>
@@ -4424,10 +4424,10 @@
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F92" t="str">
-        <v>00:01:26.05</v>
+        <v>00:01:22.38</v>
       </c>
       <c r="G92">
-        <v>217</v>
+        <v>247</v>
       </c>
       <c r="H92" s="1">
         <v>44709.99949074074</v>
@@ -4453,25 +4453,25 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B93" t="str">
         <v>100 Libre</v>
       </c>
       <c r="C93" t="str">
-        <v>IRENE RUIZ ORTIZ</v>
+        <v>CLAUDIA LATORRE MARTIN</v>
       </c>
       <c r="D93">
-        <v>2008</v>
+        <v>2009</v>
       </c>
       <c r="E93" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F93" t="str">
-        <v>00:01:26.58</v>
+        <v>00:01:25.53</v>
       </c>
       <c r="G93">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="H93" s="1">
         <v>44709.99949074074</v>
@@ -4497,13 +4497,13 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B94" t="str">
         <v>100 Libre</v>
       </c>
       <c r="C94" t="str">
-        <v>AINOHA MONASTERIO BANEGA</v>
+        <v>VALERIA RUIZ ORTIZ</v>
       </c>
       <c r="D94">
         <v>2007</v>
@@ -4512,10 +4512,10 @@
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F94" t="str">
-        <v>00:01:30.81</v>
+        <v>00:01:26.05</v>
       </c>
       <c r="G94">
-        <v>185</v>
+        <v>217</v>
       </c>
       <c r="H94" s="1">
         <v>44709.99949074074</v>
@@ -4541,28 +4541,28 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B95" t="str">
         <v>100 Libre</v>
       </c>
       <c r="C95" t="str">
-        <v>ALEXANDRA RODRIGUEZ LOPEZ</v>
+        <v>IRENE RUIZ ORTIZ</v>
       </c>
       <c r="D95">
-        <v>2000</v>
+        <v>2008</v>
       </c>
       <c r="E95" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F95" t="str">
-        <v>00:01:35.79</v>
+        <v>00:01:26.58</v>
       </c>
       <c r="G95">
-        <v>157</v>
+        <v>213</v>
       </c>
       <c r="H95" s="1">
-        <v>42385.99949074074</v>
+        <v>44709.99949074074</v>
       </c>
       <c r="I95" t="str">
         <v>Deportista</v>
@@ -4573,11 +4573,11 @@
       <c r="K95" t="str">
         <v>Manual</v>
       </c>
-      <c r="L95">
-        <v>201611612001</v>
+      <c r="L95" t="str">
+        <v>Control Libre Infantil y 7ª Control Junior y Absoluto Valencia</v>
       </c>
       <c r="M95" t="str">
-        <v>CASTELLON</v>
+        <v>Sedavi</v>
       </c>
       <c r="N95" t="str">
         <v>No</v>
@@ -4585,25 +4585,25 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B96" t="str">
         <v>100 Libre</v>
       </c>
       <c r="C96" t="str">
-        <v>ROSA MARIA YEPES GARCIA</v>
+        <v>AINOHA MONASTERIO BANEGA</v>
       </c>
       <c r="D96">
-        <v>2006</v>
+        <v>2007</v>
       </c>
       <c r="E96" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F96" t="str">
-        <v>00:01:37.02</v>
+        <v>00:01:30.81</v>
       </c>
       <c r="G96">
-        <v>151</v>
+        <v>185</v>
       </c>
       <c r="H96" s="1">
         <v>44709.99949074074</v>
@@ -4629,28 +4629,28 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>1</v>
+        <v>47</v>
       </c>
       <c r="B97" t="str">
-        <v>200 Libre</v>
+        <v>100 Libre</v>
       </c>
       <c r="C97" t="str">
-        <v>MARIA VICENTE VILLAMON</v>
+        <v>ALEXANDRA RODRIGUEZ LOPEZ</v>
       </c>
       <c r="D97">
-        <v>2008</v>
+        <v>2000</v>
       </c>
       <c r="E97" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F97" t="str">
-        <v>00:02:15.95</v>
+        <v>00:01:35.79</v>
       </c>
       <c r="G97">
-        <v>563</v>
+        <v>157</v>
       </c>
       <c r="H97" s="1">
-        <v>45696.99949074074</v>
+        <v>42385.99949074074</v>
       </c>
       <c r="I97" t="str">
         <v>Deportista</v>
@@ -4659,42 +4659,42 @@
         <v>50m</v>
       </c>
       <c r="K97" t="str">
-        <v>Electrónico</v>
-      </c>
-      <c r="L97" t="str">
-        <v>CAMPEONATO AUTONOMICO JUNIOR Y ABSOLUTO DE INVIERNO 2025 C.V.</v>
+        <v>Manual</v>
+      </c>
+      <c r="L97">
+        <v>201611612001</v>
       </c>
       <c r="M97" t="str">
-        <v>Castellón</v>
+        <v>CASTELLON</v>
       </c>
       <c r="N97" t="str">
-        <v>Sí</v>
+        <v>No</v>
       </c>
     </row>
     <row r="98">
       <c r="A98">
-        <v>2</v>
+        <v>48</v>
       </c>
       <c r="B98" t="str">
-        <v>200 Libre</v>
+        <v>100 Libre</v>
       </c>
       <c r="C98" t="str">
-        <v>LUCIA ISABEL SANCHEZ CHECA</v>
+        <v>ROSA MARIA YEPES GARCIA</v>
       </c>
       <c r="D98">
-        <v>2003</v>
+        <v>2006</v>
       </c>
       <c r="E98" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F98" t="str">
-        <v>00:02:18.04</v>
+        <v>00:01:37.02</v>
       </c>
       <c r="G98">
-        <v>537</v>
+        <v>151</v>
       </c>
       <c r="H98" s="1">
-        <v>45494.99949074074</v>
+        <v>44709.99949074074</v>
       </c>
       <c r="I98" t="str">
         <v>Deportista</v>
@@ -4703,13 +4703,13 @@
         <v>50m</v>
       </c>
       <c r="K98" t="str">
-        <v>Electrónico</v>
+        <v>Manual</v>
       </c>
       <c r="L98" t="str">
-        <v>Campeonato Autonómico Open Junior Y Absoluto de Verano</v>
+        <v>Control Libre Infantil y 7ª Control Junior y Absoluto Valencia</v>
       </c>
       <c r="M98" t="str">
-        <v>Castellón</v>
+        <v>Sedavi</v>
       </c>
       <c r="N98" t="str">
         <v>No</v>
@@ -4717,28 +4717,28 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B99" t="str">
         <v>200 Libre</v>
       </c>
       <c r="C99" t="str">
-        <v>IRENE JIMENEZ PEREZ</v>
+        <v>MARIA VICENTE VILLAMON</v>
       </c>
       <c r="D99">
-        <v>1992</v>
+        <v>2008</v>
       </c>
       <c r="E99" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F99" t="str">
-        <v>00:02:22.94</v>
+        <v>00:02:15.95</v>
       </c>
       <c r="G99">
-        <v>484</v>
+        <v>563</v>
       </c>
       <c r="H99" s="1">
-        <v>43807.99949074074</v>
+        <v>45696.99949074074</v>
       </c>
       <c r="I99" t="str">
         <v>Deportista</v>
@@ -4750,39 +4750,39 @@
         <v>Electrónico</v>
       </c>
       <c r="L99" t="str">
-        <v>XVI Trofeo Internacional Castalia-Castellón 2019</v>
+        <v>CAMPEONATO AUTONOMICO JUNIOR Y ABSOLUTO DE INVIERNO 2025 C.V.</v>
       </c>
       <c r="M99" t="str">
         <v>Castellón</v>
       </c>
       <c r="N99" t="str">
-        <v>No</v>
+        <v>Sí</v>
       </c>
     </row>
     <row r="100">
       <c r="A100">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B100" t="str">
         <v>200 Libre</v>
       </c>
       <c r="C100" t="str">
-        <v>ISABEL MORAGUES GINER</v>
+        <v>LUCIA ISABEL SANCHEZ CHECA</v>
       </c>
       <c r="D100">
-        <v>2005</v>
+        <v>2003</v>
       </c>
       <c r="E100" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F100" t="str">
-        <v>00:02:23.03</v>
+        <v>00:02:18.04</v>
       </c>
       <c r="G100">
-        <v>483</v>
+        <v>537</v>
       </c>
       <c r="H100" s="1">
-        <v>45682.99949074074</v>
+        <v>45494.99949074074</v>
       </c>
       <c r="I100" t="str">
         <v>Deportista</v>
@@ -4794,10 +4794,10 @@
         <v>Electrónico</v>
       </c>
       <c r="L100" t="str">
-        <v>XXX MEMORIAL PASCUAL ROMAN</v>
+        <v>Campeonato Autonómico Open Junior Y Absoluto de Verano</v>
       </c>
       <c r="M100" t="str">
-        <v>Elche</v>
+        <v>Castellón</v>
       </c>
       <c r="N100" t="str">
         <v>No</v>
@@ -4805,28 +4805,28 @@
     </row>
     <row r="101">
       <c r="A101">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B101" t="str">
         <v>200 Libre</v>
       </c>
       <c r="C101" t="str">
-        <v>ALBA IZQUIERDO LOPEZ</v>
+        <v>MARIA ANGELES GRASSO CUENCA</v>
       </c>
       <c r="D101">
-        <v>2003</v>
+        <v>2011</v>
       </c>
       <c r="E101" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F101" t="str">
-        <v>00:02:23.10</v>
+        <v>00:02:22.21</v>
       </c>
       <c r="G101">
-        <v>482</v>
+        <v>492</v>
       </c>
       <c r="H101" s="1">
-        <v>44745.99949074074</v>
+        <v>46201.99949074074</v>
       </c>
       <c r="I101" t="str">
         <v>Deportista</v>
@@ -4838,10 +4838,10 @@
         <v>Electrónico</v>
       </c>
       <c r="L101" t="str">
-        <v>Campeonato Autonómico Jr y Abs de Verano OPEN P50</v>
+        <v>CAMPEONATO AUTONOMICO INFANTIL DE VERANO DE LA C.V. 2026</v>
       </c>
       <c r="M101" t="str">
-        <v>Castellón</v>
+        <v>CASTELLON</v>
       </c>
       <c r="N101" t="str">
         <v>No</v>
@@ -4849,28 +4849,28 @@
     </row>
     <row r="102">
       <c r="A102">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B102" t="str">
         <v>200 Libre</v>
       </c>
       <c r="C102" t="str">
-        <v>MANUELA RADEANU</v>
+        <v>IRENE JIMENEZ PEREZ</v>
       </c>
       <c r="D102">
-        <v>2007</v>
+        <v>1992</v>
       </c>
       <c r="E102" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F102" t="str">
-        <v>00:02:27.90</v>
+        <v>00:02:22.94</v>
       </c>
       <c r="G102">
-        <v>437</v>
+        <v>484</v>
       </c>
       <c r="H102" s="1">
-        <v>44381.99949074074</v>
+        <v>43807.99949074074</v>
       </c>
       <c r="I102" t="str">
         <v>Deportista</v>
@@ -4882,10 +4882,10 @@
         <v>Electrónico</v>
       </c>
       <c r="L102" t="str">
-        <v>Autonomico Infantil Verano</v>
+        <v>XVI Trofeo Internacional Castalia-Castellón 2019</v>
       </c>
       <c r="M102" t="str">
-        <v>Castellon</v>
+        <v>Castellón</v>
       </c>
       <c r="N102" t="str">
         <v>No</v>
@@ -4893,28 +4893,28 @@
     </row>
     <row r="103">
       <c r="A103">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B103" t="str">
         <v>200 Libre</v>
       </c>
       <c r="C103" t="str">
-        <v>SOFIA CALABUIG MARTINEZ</v>
+        <v>ISABEL MORAGUES GINER</v>
       </c>
       <c r="D103">
-        <v>2011</v>
+        <v>2005</v>
       </c>
       <c r="E103" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F103" t="str">
-        <v>00:02:28.34</v>
+        <v>00:02:23.03</v>
       </c>
       <c r="G103">
-        <v>433</v>
+        <v>483</v>
       </c>
       <c r="H103" s="1">
-        <v>45836.99949074074</v>
+        <v>45682.99949074074</v>
       </c>
       <c r="I103" t="str">
         <v>Deportista</v>
@@ -4926,39 +4926,39 @@
         <v>Electrónico</v>
       </c>
       <c r="L103" t="str">
-        <v>CAMPEONATO AUTONOMICO INFANTIL DE VERANO 2025</v>
+        <v>XXX MEMORIAL PASCUAL ROMAN</v>
       </c>
       <c r="M103" t="str">
-        <v>Castellón</v>
+        <v>Elche</v>
       </c>
       <c r="N103" t="str">
-        <v>Sí</v>
+        <v>No</v>
       </c>
     </row>
     <row r="104">
       <c r="A104">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B104" t="str">
         <v>200 Libre</v>
       </c>
       <c r="C104" t="str">
-        <v>ANGELS REQUENA MARTINEZ</v>
+        <v>ALBA IZQUIERDO LOPEZ</v>
       </c>
       <c r="D104">
-        <v>2012</v>
+        <v>2003</v>
       </c>
       <c r="E104" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F104" t="str">
-        <v>00:02:28.53</v>
+        <v>00:02:23.10</v>
       </c>
       <c r="G104">
-        <v>431</v>
+        <v>482</v>
       </c>
       <c r="H104" s="1">
-        <v>46081.99949074074</v>
+        <v>44745.99949074074</v>
       </c>
       <c r="I104" t="str">
         <v>Deportista</v>
@@ -4970,39 +4970,39 @@
         <v>Electrónico</v>
       </c>
       <c r="L104" t="str">
-        <v>CAMPEONATO AUTONOMICO INFANTIL DE INVIERNO 2026</v>
+        <v>Campeonato Autonómico Jr y Abs de Verano OPEN P50</v>
       </c>
       <c r="M104" t="str">
-        <v>CASTELLÓN</v>
+        <v>Castellón</v>
       </c>
       <c r="N104" t="str">
-        <v>Sí</v>
+        <v>No</v>
       </c>
     </row>
     <row r="105">
       <c r="A105">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B105" t="str">
         <v>200 Libre</v>
       </c>
       <c r="C105" t="str">
-        <v>LUCIA CUEVAS CASAS</v>
+        <v>MANUELA RADEANU</v>
       </c>
       <c r="D105">
-        <v>2006</v>
+        <v>2007</v>
       </c>
       <c r="E105" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F105" t="str">
-        <v>00:02:28.76</v>
+        <v>00:02:27.90</v>
       </c>
       <c r="G105">
-        <v>429</v>
+        <v>437</v>
       </c>
       <c r="H105" s="1">
-        <v>44975.99949074074</v>
+        <v>44381.99949074074</v>
       </c>
       <c r="I105" t="str">
         <v>Deportista</v>
@@ -5014,10 +5014,10 @@
         <v>Electrónico</v>
       </c>
       <c r="L105" t="str">
-        <v>Trofeo Internacional XXVIII Memorial Pascual Roman</v>
+        <v>Autonomico Infantil Verano</v>
       </c>
       <c r="M105" t="str">
-        <v>Elche</v>
+        <v>Castellon</v>
       </c>
       <c r="N105" t="str">
         <v>No</v>
@@ -5025,28 +5025,28 @@
     </row>
     <row r="106">
       <c r="A106">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B106" t="str">
         <v>200 Libre</v>
       </c>
       <c r="C106" t="str">
-        <v>INES PEDRERO MARTINEZ</v>
+        <v>SOFIA CALABUIG MARTINEZ</v>
       </c>
       <c r="D106">
-        <v>2008</v>
+        <v>2011</v>
       </c>
       <c r="E106" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F106" t="str">
-        <v>00:02:29.52</v>
+        <v>00:02:28.34</v>
       </c>
       <c r="G106">
-        <v>423</v>
+        <v>433</v>
       </c>
       <c r="H106" s="1">
-        <v>45108.99949074074</v>
+        <v>45836.99949074074</v>
       </c>
       <c r="I106" t="str">
         <v>Deportista</v>
@@ -5058,39 +5058,39 @@
         <v>Electrónico</v>
       </c>
       <c r="L106" t="str">
-        <v>Campeonato Autonomico Infantil de Verano</v>
+        <v>CAMPEONATO AUTONOMICO INFANTIL DE VERANO 2025</v>
       </c>
       <c r="M106" t="str">
-        <v>ELDA</v>
+        <v>Castellón</v>
       </c>
       <c r="N106" t="str">
-        <v>No</v>
+        <v>Sí</v>
       </c>
     </row>
     <row r="107">
       <c r="A107">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B107" t="str">
         <v>200 Libre</v>
       </c>
       <c r="C107" t="str">
-        <v>MARIA ANGELES GRASSO CUENCA</v>
+        <v>ANGELS REQUENA MARTINEZ</v>
       </c>
       <c r="D107">
-        <v>2011</v>
+        <v>2012</v>
       </c>
       <c r="E107" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F107" t="str">
-        <v>00:02:30.08</v>
+        <v>00:02:28.53</v>
       </c>
       <c r="G107">
-        <v>418</v>
+        <v>431</v>
       </c>
       <c r="H107" s="1">
-        <v>46082.99949074074</v>
+        <v>46081.99949074074</v>
       </c>
       <c r="I107" t="str">
         <v>Deportista</v>
@@ -5108,33 +5108,33 @@
         <v>CASTELLÓN</v>
       </c>
       <c r="N107" t="str">
-        <v>No</v>
+        <v>Sí</v>
       </c>
     </row>
     <row r="108">
       <c r="A108">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B108" t="str">
         <v>200 Libre</v>
       </c>
       <c r="C108" t="str">
-        <v>ARIADNA MANZANEDA GARCIA</v>
+        <v>LUCIA CUEVAS CASAS</v>
       </c>
       <c r="D108">
-        <v>2012</v>
+        <v>2006</v>
       </c>
       <c r="E108" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F108" t="str">
-        <v>00:02:30.21</v>
+        <v>00:02:28.76</v>
       </c>
       <c r="G108">
-        <v>417</v>
+        <v>429</v>
       </c>
       <c r="H108" s="1">
-        <v>46173.99949074074</v>
+        <v>44975.99949074074</v>
       </c>
       <c r="I108" t="str">
         <v>Deportista</v>
@@ -5143,13 +5143,13 @@
         <v>50m</v>
       </c>
       <c r="K108" t="str">
-        <v>Manual</v>
+        <v>Electrónico</v>
       </c>
       <c r="L108" t="str">
-        <v>LVI TROFEU SANT PASCUAL XXXVII MEMORIAL JOSE VICENTE MARTI BARRACHINA</v>
+        <v>Trofeo Internacional XXVIII Memorial Pascual Roman</v>
       </c>
       <c r="M108" t="str">
-        <v>Vila-Real</v>
+        <v>Elche</v>
       </c>
       <c r="N108" t="str">
         <v>No</v>
@@ -5157,13 +5157,13 @@
     </row>
     <row r="109">
       <c r="A109">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B109" t="str">
         <v>200 Libre</v>
       </c>
       <c r="C109" t="str">
-        <v>SOFIA VICTORIA ESTACIO ROMAN</v>
+        <v>INES PEDRERO MARTINEZ</v>
       </c>
       <c r="D109">
         <v>2008</v>
@@ -5172,13 +5172,13 @@
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F109" t="str">
-        <v>00:02:31.79</v>
+        <v>00:02:29.52</v>
       </c>
       <c r="G109">
-        <v>404</v>
+        <v>423</v>
       </c>
       <c r="H109" s="1">
-        <v>45682.99949074074</v>
+        <v>45108.99949074074</v>
       </c>
       <c r="I109" t="str">
         <v>Deportista</v>
@@ -5190,10 +5190,10 @@
         <v>Electrónico</v>
       </c>
       <c r="L109" t="str">
-        <v>XXX MEMORIAL PASCUAL ROMAN</v>
+        <v>Campeonato Autonomico Infantil de Verano</v>
       </c>
       <c r="M109" t="str">
-        <v>Elche</v>
+        <v>ELDA</v>
       </c>
       <c r="N109" t="str">
         <v>No</v>
@@ -5201,28 +5201,28 @@
     </row>
     <row r="110">
       <c r="A110">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B110" t="str">
         <v>200 Libre</v>
       </c>
       <c r="C110" t="str">
-        <v>JUDITH HERGUETA VICIANO</v>
+        <v>ARIADNA MANZANEDA GARCIA</v>
       </c>
       <c r="D110">
-        <v>2008</v>
+        <v>2012</v>
       </c>
       <c r="E110" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F110" t="str">
-        <v>00:02:33.29</v>
+        <v>00:02:30.21</v>
       </c>
       <c r="G110">
-        <v>392</v>
+        <v>417</v>
       </c>
       <c r="H110" s="1">
-        <v>45682.99949074074</v>
+        <v>46173.99949074074</v>
       </c>
       <c r="I110" t="str">
         <v>Deportista</v>
@@ -5231,13 +5231,13 @@
         <v>50m</v>
       </c>
       <c r="K110" t="str">
-        <v>Electrónico</v>
+        <v>Manual</v>
       </c>
       <c r="L110" t="str">
-        <v>XXX MEMORIAL PASCUAL ROMAN</v>
+        <v>LVI TROFEU SANT PASCUAL XXXVII MEMORIAL JOSE VICENTE MARTI BARRACHINA</v>
       </c>
       <c r="M110" t="str">
-        <v>Elche</v>
+        <v>Vila-Real</v>
       </c>
       <c r="N110" t="str">
         <v>No</v>
@@ -5245,28 +5245,28 @@
     </row>
     <row r="111">
       <c r="A111">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B111" t="str">
         <v>200 Libre</v>
       </c>
       <c r="C111" t="str">
-        <v>VEGA ALCANTARA SANTA CRUZ</v>
+        <v>SOFIA VICTORIA ESTACIO ROMAN</v>
       </c>
       <c r="D111">
-        <v>2011</v>
+        <v>2008</v>
       </c>
       <c r="E111" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F111" t="str">
-        <v>00:02:34.73</v>
+        <v>00:02:31.79</v>
       </c>
       <c r="G111">
-        <v>382</v>
+        <v>404</v>
       </c>
       <c r="H111" s="1">
-        <v>46046.99949074074</v>
+        <v>45682.99949074074</v>
       </c>
       <c r="I111" t="str">
         <v>Deportista</v>
@@ -5278,7 +5278,7 @@
         <v>Electrónico</v>
       </c>
       <c r="L111" t="str">
-        <v>TROFEO INTERNACIONAL XXXI MEMORIAL PASCUAL ROMAN</v>
+        <v>XXX MEMORIAL PASCUAL ROMAN</v>
       </c>
       <c r="M111" t="str">
         <v>Elche</v>
@@ -5289,28 +5289,28 @@
     </row>
     <row r="112">
       <c r="A112">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B112" t="str">
         <v>200 Libre</v>
       </c>
       <c r="C112" t="str">
-        <v>CAMILA GUEVARA PEROZO</v>
+        <v>JUDITH HERGUETA VICIANO</v>
       </c>
       <c r="D112">
-        <v>2010</v>
+        <v>2008</v>
       </c>
       <c r="E112" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F112" t="str">
-        <v>00:02:35.55</v>
+        <v>00:02:33.29</v>
       </c>
       <c r="G112">
-        <v>376</v>
+        <v>392</v>
       </c>
       <c r="H112" s="1">
-        <v>45837.99949074074</v>
+        <v>45682.99949074074</v>
       </c>
       <c r="I112" t="str">
         <v>Deportista</v>
@@ -5322,10 +5322,10 @@
         <v>Electrónico</v>
       </c>
       <c r="L112" t="str">
-        <v>CAMPEONATO AUTONOMICO INFANTIL DE VERANO 2025</v>
+        <v>XXX MEMORIAL PASCUAL ROMAN</v>
       </c>
       <c r="M112" t="str">
-        <v>Castellón</v>
+        <v>Elche</v>
       </c>
       <c r="N112" t="str">
         <v>No</v>
@@ -5333,28 +5333,28 @@
     </row>
     <row r="113">
       <c r="A113">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B113" t="str">
         <v>200 Libre</v>
       </c>
       <c r="C113" t="str">
-        <v>MARIA MENDOZA GOMEZ</v>
+        <v>VEGA ALCANTARA SANTA CRUZ</v>
       </c>
       <c r="D113">
-        <v>2003</v>
+        <v>2011</v>
       </c>
       <c r="E113" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F113" t="str">
-        <v>00:02:39.52</v>
+        <v>00:02:34.73</v>
       </c>
       <c r="G113">
-        <v>348</v>
+        <v>382</v>
       </c>
       <c r="H113" s="1">
-        <v>43638.99949074074</v>
+        <v>46046.99949074074</v>
       </c>
       <c r="I113" t="str">
         <v>Deportista</v>
@@ -5363,13 +5363,13 @@
         <v>50m</v>
       </c>
       <c r="K113" t="str">
-        <v>Manual</v>
+        <v>Electrónico</v>
       </c>
       <c r="L113" t="str">
-        <v>7ª Jornada Control infa y mayores</v>
+        <v>TROFEO INTERNACIONAL XXXI MEMORIAL PASCUAL ROMAN</v>
       </c>
       <c r="M113" t="str">
-        <v>Moncada</v>
+        <v>Elche</v>
       </c>
       <c r="N113" t="str">
         <v>No</v>
@@ -5377,13 +5377,13 @@
     </row>
     <row r="114">
       <c r="A114">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B114" t="str">
         <v>200 Libre</v>
       </c>
       <c r="C114" t="str">
-        <v>PAOLA MEIJIDE VILLANUEVA</v>
+        <v>CAMILA GUEVARA PEROZO</v>
       </c>
       <c r="D114">
         <v>2010</v>
@@ -5392,13 +5392,13 @@
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F114" t="str">
-        <v>00:02:40.85</v>
+        <v>00:02:35.55</v>
       </c>
       <c r="G114">
-        <v>340</v>
+        <v>376</v>
       </c>
       <c r="H114" s="1">
-        <v>46173.99949074074</v>
+        <v>45837.99949074074</v>
       </c>
       <c r="I114" t="str">
         <v>Deportista</v>
@@ -5407,13 +5407,13 @@
         <v>50m</v>
       </c>
       <c r="K114" t="str">
-        <v>Manual</v>
+        <v>Electrónico</v>
       </c>
       <c r="L114" t="str">
-        <v>LVI TROFEU SANT PASCUAL XXXVII MEMORIAL JOSE VICENTE MARTI BARRACHINA</v>
+        <v>CAMPEONATO AUTONOMICO INFANTIL DE VERANO 2025</v>
       </c>
       <c r="M114" t="str">
-        <v>Vila-Real</v>
+        <v>Castellón</v>
       </c>
       <c r="N114" t="str">
         <v>No</v>
@@ -5421,28 +5421,28 @@
     </row>
     <row r="115">
       <c r="A115">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B115" t="str">
         <v>200 Libre</v>
       </c>
       <c r="C115" t="str">
-        <v>APPOLINARIIA KOROLEVA</v>
+        <v>LOLA FERRI BELLVER</v>
       </c>
       <c r="D115">
-        <v>2011</v>
+        <v>2012</v>
       </c>
       <c r="E115" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F115" t="str">
-        <v>00:02:41.49</v>
+        <v>00:02:36.64</v>
       </c>
       <c r="G115">
-        <v>336</v>
+        <v>368</v>
       </c>
       <c r="H115" s="1">
-        <v>45710.99949074074</v>
+        <v>46200.99949074074</v>
       </c>
       <c r="I115" t="str">
         <v>Deportista</v>
@@ -5454,10 +5454,10 @@
         <v>Electrónico</v>
       </c>
       <c r="L115" t="str">
-        <v>CAMPEONATO AUTONOMICO INFANTIL DE INVIERNO 2025 C.V.</v>
+        <v>CAMPEONATO AUTONOMICO INFANTIL DE VERANO DE LA C.V. 2026</v>
       </c>
       <c r="M115" t="str">
-        <v>ELCHE</v>
+        <v>CASTELLON</v>
       </c>
       <c r="N115" t="str">
         <v>Sí</v>
@@ -5465,28 +5465,28 @@
     </row>
     <row r="116">
       <c r="A116">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B116" t="str">
         <v>200 Libre</v>
       </c>
       <c r="C116" t="str">
-        <v>ROCIO MARTINEZ GONZALEZ</v>
+        <v>MARIA MENDOZA GOMEZ</v>
       </c>
       <c r="D116">
-        <v>2011</v>
+        <v>2003</v>
       </c>
       <c r="E116" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F116" t="str">
-        <v>00:02:44.65</v>
+        <v>00:02:39.52</v>
       </c>
       <c r="G116">
-        <v>317</v>
+        <v>348</v>
       </c>
       <c r="H116" s="1">
-        <v>45681.99949074074</v>
+        <v>43638.99949074074</v>
       </c>
       <c r="I116" t="str">
         <v>Deportista</v>
@@ -5495,42 +5495,42 @@
         <v>50m</v>
       </c>
       <c r="K116" t="str">
-        <v>Electrónico</v>
+        <v>Manual</v>
       </c>
       <c r="L116" t="str">
-        <v>XXX MEMORIAL PASCUAL ROMAN</v>
+        <v>7ª Jornada Control infa y mayores</v>
       </c>
       <c r="M116" t="str">
-        <v>Elche</v>
+        <v>Moncada</v>
       </c>
       <c r="N116" t="str">
-        <v>Sí</v>
+        <v>No</v>
       </c>
     </row>
     <row r="117">
       <c r="A117">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B117" t="str">
         <v>200 Libre</v>
       </c>
       <c r="C117" t="str">
-        <v>MARTINA GOMEZ GONZALEZ</v>
+        <v>PAOLA MEIJIDE VILLANUEVA</v>
       </c>
       <c r="D117">
-        <v>2007</v>
+        <v>2010</v>
       </c>
       <c r="E117" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F117" t="str">
-        <v>00:02:45.68</v>
+        <v>00:02:40.85</v>
       </c>
       <c r="G117">
-        <v>311</v>
+        <v>340</v>
       </c>
       <c r="H117" s="1">
-        <v>45326.99949074074</v>
+        <v>46173.99949074074</v>
       </c>
       <c r="I117" t="str">
         <v>Deportista</v>
@@ -5539,13 +5539,13 @@
         <v>50m</v>
       </c>
       <c r="K117" t="str">
-        <v>Electrónico</v>
+        <v>Manual</v>
       </c>
       <c r="L117" t="str">
-        <v>Campeonato Autonómico Open Jr Y Absoluto de Invierno</v>
+        <v>LVI TROFEU SANT PASCUAL XXXVII MEMORIAL JOSE VICENTE MARTI BARRACHINA</v>
       </c>
       <c r="M117" t="str">
-        <v>Castellon</v>
+        <v>Vila-Real</v>
       </c>
       <c r="N117" t="str">
         <v>No</v>
@@ -5553,13 +5553,13 @@
     </row>
     <row r="118">
       <c r="A118">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B118" t="str">
         <v>200 Libre</v>
       </c>
       <c r="C118" t="str">
-        <v>DARIS IVANOVA STOYANOVA</v>
+        <v>APPOLINARIIA KOROLEVA</v>
       </c>
       <c r="D118">
         <v>2011</v>
@@ -5568,13 +5568,13 @@
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F118" t="str">
-        <v>00:02:51.24</v>
+        <v>00:02:41.49</v>
       </c>
       <c r="G118">
-        <v>282</v>
+        <v>336</v>
       </c>
       <c r="H118" s="1">
-        <v>45682.99949074074</v>
+        <v>45710.99949074074</v>
       </c>
       <c r="I118" t="str">
         <v>Deportista</v>
@@ -5586,39 +5586,39 @@
         <v>Electrónico</v>
       </c>
       <c r="L118" t="str">
-        <v>XXX MEMORIAL PASCUAL ROMAN</v>
+        <v>CAMPEONATO AUTONOMICO INFANTIL DE INVIERNO 2025 C.V.</v>
       </c>
       <c r="M118" t="str">
-        <v>Elche</v>
+        <v>ELCHE</v>
       </c>
       <c r="N118" t="str">
-        <v>No</v>
+        <v>Sí</v>
       </c>
     </row>
     <row r="119">
       <c r="A119">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B119" t="str">
         <v>200 Libre</v>
       </c>
       <c r="C119" t="str">
-        <v>ALESSIA PAFUNDI</v>
+        <v>ROCIO MARTINEZ GONZALEZ</v>
       </c>
       <c r="D119">
-        <v>2000</v>
+        <v>2011</v>
       </c>
       <c r="E119" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F119" t="str">
-        <v>00:03:01.84</v>
+        <v>00:02:44.65</v>
       </c>
       <c r="G119">
-        <v>235</v>
+        <v>317</v>
       </c>
       <c r="H119" s="1">
-        <v>42539.99949074074</v>
+        <v>45681.99949074074</v>
       </c>
       <c r="I119" t="str">
         <v>Deportista</v>
@@ -5627,27 +5627,27 @@
         <v>50m</v>
       </c>
       <c r="K119" t="str">
-        <v>Manual</v>
+        <v>Electrónico</v>
       </c>
       <c r="L119" t="str">
-        <v>8º CONTROL PROVINCIAL A+B+C+D (4-3)</v>
+        <v>XXX MEMORIAL PASCUAL ROMAN</v>
       </c>
       <c r="M119" t="str">
-        <v>SEDAVI</v>
+        <v>Elche</v>
       </c>
       <c r="N119" t="str">
-        <v>No</v>
+        <v>Sí</v>
       </c>
     </row>
     <row r="120">
       <c r="A120">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B120" t="str">
         <v>200 Libre</v>
       </c>
       <c r="C120" t="str">
-        <v>SANDRA DOMINGUEZ VALERO</v>
+        <v>MARTINA GOMEZ GONZALEZ</v>
       </c>
       <c r="D120">
         <v>2007</v>
@@ -5656,13 +5656,13 @@
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F120" t="str">
-        <v>00:03:02.07</v>
+        <v>00:02:45.68</v>
       </c>
       <c r="G120">
-        <v>234</v>
+        <v>311</v>
       </c>
       <c r="H120" s="1">
-        <v>44709.99949074074</v>
+        <v>45326.99949074074</v>
       </c>
       <c r="I120" t="str">
         <v>Deportista</v>
@@ -5671,13 +5671,13 @@
         <v>50m</v>
       </c>
       <c r="K120" t="str">
-        <v>Manual</v>
+        <v>Electrónico</v>
       </c>
       <c r="L120" t="str">
-        <v>Control Libre Infantil y 7ª Control Junior y Absoluto Valencia</v>
+        <v>Campeonato Autonómico Open Jr Y Absoluto de Invierno</v>
       </c>
       <c r="M120" t="str">
-        <v>Sedavi</v>
+        <v>Castellon</v>
       </c>
       <c r="N120" t="str">
         <v>No</v>
@@ -5685,28 +5685,28 @@
     </row>
     <row r="121">
       <c r="A121">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B121" t="str">
         <v>200 Libre</v>
       </c>
       <c r="C121" t="str">
-        <v>IRENE TAMARIT MUNERA</v>
+        <v>DARIS IVANOVA STOYANOVA</v>
       </c>
       <c r="D121">
-        <v>2008</v>
+        <v>2011</v>
       </c>
       <c r="E121" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F121" t="str">
-        <v>00:03:02.09</v>
+        <v>00:02:51.24</v>
       </c>
       <c r="G121">
-        <v>234</v>
+        <v>282</v>
       </c>
       <c r="H121" s="1">
-        <v>44709.99949074074</v>
+        <v>45682.99949074074</v>
       </c>
       <c r="I121" t="str">
         <v>Deportista</v>
@@ -5715,13 +5715,13 @@
         <v>50m</v>
       </c>
       <c r="K121" t="str">
-        <v>Manual</v>
+        <v>Electrónico</v>
       </c>
       <c r="L121" t="str">
-        <v>Control Libre Infantil y 7ª Control Junior y Absoluto Valencia</v>
+        <v>XXX MEMORIAL PASCUAL ROMAN</v>
       </c>
       <c r="M121" t="str">
-        <v>Sedavi</v>
+        <v>Elche</v>
       </c>
       <c r="N121" t="str">
         <v>No</v>
@@ -5729,28 +5729,28 @@
     </row>
     <row r="122">
       <c r="A122">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B122" t="str">
         <v>200 Libre</v>
       </c>
       <c r="C122" t="str">
-        <v>INGRID MONTALVA TERCERO</v>
+        <v>ALESSIA PAFUNDI</v>
       </c>
       <c r="D122">
-        <v>2008</v>
+        <v>2000</v>
       </c>
       <c r="E122" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F122" t="str">
-        <v>00:03:12.65</v>
+        <v>00:03:01.84</v>
       </c>
       <c r="G122">
-        <v>198</v>
+        <v>235</v>
       </c>
       <c r="H122" s="1">
-        <v>44709.99949074074</v>
+        <v>42539.99949074074</v>
       </c>
       <c r="I122" t="str">
         <v>Deportista</v>
@@ -5762,10 +5762,10 @@
         <v>Manual</v>
       </c>
       <c r="L122" t="str">
-        <v>Control Libre Infantil y 7ª Control Junior y Absoluto Valencia</v>
+        <v>8º CONTROL PROVINCIAL A+B+C+D (4-3)</v>
       </c>
       <c r="M122" t="str">
-        <v>Sedavi</v>
+        <v>SEDAVI</v>
       </c>
       <c r="N122" t="str">
         <v>No</v>
@@ -5773,28 +5773,28 @@
     </row>
     <row r="123">
       <c r="A123">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B123" t="str">
         <v>200 Libre</v>
       </c>
       <c r="C123" t="str">
-        <v>IRENE RUIZ ORTIZ</v>
+        <v>SANDRA DOMINGUEZ VALERO</v>
       </c>
       <c r="D123">
-        <v>2008</v>
+        <v>2007</v>
       </c>
       <c r="E123" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F123" t="str">
-        <v>00:03:14.01</v>
+        <v>00:03:02.07</v>
       </c>
       <c r="G123">
-        <v>194</v>
+        <v>234</v>
       </c>
       <c r="H123" s="1">
-        <v>44612.99949074074</v>
+        <v>44709.99949074074</v>
       </c>
       <c r="I123" t="str">
         <v>Deportista</v>
@@ -5806,10 +5806,10 @@
         <v>Manual</v>
       </c>
       <c r="L123" t="str">
-        <v>4º Control Infantil Junior y Absoluto Castellón</v>
+        <v>Control Libre Infantil y 7ª Control Junior y Absoluto Valencia</v>
       </c>
       <c r="M123" t="str">
-        <v>Castellón</v>
+        <v>Sedavi</v>
       </c>
       <c r="N123" t="str">
         <v>No</v>
@@ -5817,25 +5817,25 @@
     </row>
     <row r="124">
       <c r="A124">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B124" t="str">
         <v>200 Libre</v>
       </c>
       <c r="C124" t="str">
-        <v>CLAUDIA LATORRE MARTIN</v>
+        <v>IRENE TAMARIT MUNERA</v>
       </c>
       <c r="D124">
-        <v>2009</v>
+        <v>2008</v>
       </c>
       <c r="E124" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F124" t="str">
-        <v>00:03:18.03</v>
+        <v>00:03:02.09</v>
       </c>
       <c r="G124">
-        <v>182</v>
+        <v>234</v>
       </c>
       <c r="H124" s="1">
         <v>44709.99949074074</v>
@@ -5861,28 +5861,28 @@
     </row>
     <row r="125">
       <c r="A125">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B125" t="str">
         <v>200 Libre</v>
       </c>
       <c r="C125" t="str">
-        <v>VALERIA RUIZ ORTIZ</v>
+        <v>INGRID MONTALVA TERCERO</v>
       </c>
       <c r="D125">
-        <v>2007</v>
+        <v>2008</v>
       </c>
       <c r="E125" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F125" t="str">
-        <v>00:03:21.32</v>
+        <v>00:03:12.65</v>
       </c>
       <c r="G125">
-        <v>173</v>
+        <v>198</v>
       </c>
       <c r="H125" s="1">
-        <v>44612.99949074074</v>
+        <v>44709.99949074074</v>
       </c>
       <c r="I125" t="str">
         <v>Deportista</v>
@@ -5894,10 +5894,10 @@
         <v>Manual</v>
       </c>
       <c r="L125" t="str">
-        <v>4º Control Infantil Junior y Absoluto Castellón</v>
+        <v>Control Libre Infantil y 7ª Control Junior y Absoluto Valencia</v>
       </c>
       <c r="M125" t="str">
-        <v>Castellón</v>
+        <v>Sedavi</v>
       </c>
       <c r="N125" t="str">
         <v>No</v>
@@ -5905,28 +5905,28 @@
     </row>
     <row r="126">
       <c r="A126">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B126" t="str">
         <v>200 Libre</v>
       </c>
       <c r="C126" t="str">
-        <v>AINOHA MONASTERIO BANEGA</v>
+        <v>IRENE RUIZ ORTIZ</v>
       </c>
       <c r="D126">
-        <v>2007</v>
+        <v>2008</v>
       </c>
       <c r="E126" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F126" t="str">
-        <v>00:03:23.33</v>
+        <v>00:03:14.01</v>
       </c>
       <c r="G126">
-        <v>168</v>
+        <v>194</v>
       </c>
       <c r="H126" s="1">
-        <v>44709.99949074074</v>
+        <v>44612.99949074074</v>
       </c>
       <c r="I126" t="str">
         <v>Deportista</v>
@@ -5938,10 +5938,10 @@
         <v>Manual</v>
       </c>
       <c r="L126" t="str">
-        <v>Control Libre Infantil y 7ª Control Junior y Absoluto Valencia</v>
+        <v>4º Control Infantil Junior y Absoluto Castellón</v>
       </c>
       <c r="M126" t="str">
-        <v>Sedavi</v>
+        <v>Castellón</v>
       </c>
       <c r="N126" t="str">
         <v>No</v>
@@ -5949,13 +5949,13 @@
     </row>
     <row r="127">
       <c r="A127">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B127" t="str">
         <v>200 Libre</v>
       </c>
       <c r="C127" t="str">
-        <v>IRENE BELLVER OJEDA</v>
+        <v>CLAUDIA LATORRE MARTIN</v>
       </c>
       <c r="D127">
         <v>2009</v>
@@ -5964,13 +5964,13 @@
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F127" t="str">
-        <v>00:03:33.92</v>
+        <v>00:03:18.03</v>
       </c>
       <c r="G127">
-        <v>144</v>
+        <v>182</v>
       </c>
       <c r="H127" s="1">
-        <v>44612.99949074074</v>
+        <v>44709.99949074074</v>
       </c>
       <c r="I127" t="str">
         <v>Deportista</v>
@@ -5982,10 +5982,10 @@
         <v>Manual</v>
       </c>
       <c r="L127" t="str">
-        <v>4º Control Infantil Junior y Absoluto Castellón</v>
+        <v>Control Libre Infantil y 7ª Control Junior y Absoluto Valencia</v>
       </c>
       <c r="M127" t="str">
-        <v>Castellón</v>
+        <v>Sedavi</v>
       </c>
       <c r="N127" t="str">
         <v>No</v>
@@ -5993,28 +5993,28 @@
     </row>
     <row r="128">
       <c r="A128">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="B128" t="str">
-        <v>400 Libre</v>
+        <v>200 Libre</v>
       </c>
       <c r="C128" t="str">
-        <v>ISABEL MORAGUES GINER</v>
+        <v>VALERIA RUIZ ORTIZ</v>
       </c>
       <c r="D128">
-        <v>2005</v>
+        <v>2007</v>
       </c>
       <c r="E128" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F128" t="str">
-        <v>00:04:57.74</v>
+        <v>00:03:21.32</v>
       </c>
       <c r="G128">
-        <v>494</v>
+        <v>173</v>
       </c>
       <c r="H128" s="1">
-        <v>45682.99949074074</v>
+        <v>44612.99949074074</v>
       </c>
       <c r="I128" t="str">
         <v>Deportista</v>
@@ -6023,13 +6023,13 @@
         <v>50m</v>
       </c>
       <c r="K128" t="str">
-        <v>Electrónico</v>
+        <v>Manual</v>
       </c>
       <c r="L128" t="str">
-        <v>XXX MEMORIAL PASCUAL ROMAN</v>
+        <v>4º Control Infantil Junior y Absoluto Castellón</v>
       </c>
       <c r="M128" t="str">
-        <v>Elche</v>
+        <v>Castellón</v>
       </c>
       <c r="N128" t="str">
         <v>No</v>
@@ -6037,28 +6037,28 @@
     </row>
     <row r="129">
       <c r="A129">
-        <v>2</v>
+        <v>31</v>
       </c>
       <c r="B129" t="str">
-        <v>400 Libre</v>
+        <v>200 Libre</v>
       </c>
       <c r="C129" t="str">
-        <v>ALBA IZQUIERDO LOPEZ</v>
+        <v>AINOHA MONASTERIO BANEGA</v>
       </c>
       <c r="D129">
-        <v>2003</v>
+        <v>2007</v>
       </c>
       <c r="E129" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F129" t="str">
-        <v>00:05:07.72</v>
+        <v>00:03:23.33</v>
       </c>
       <c r="G129">
-        <v>448</v>
+        <v>168</v>
       </c>
       <c r="H129" s="1">
-        <v>45094.99949074074</v>
+        <v>44709.99949074074</v>
       </c>
       <c r="I129" t="str">
         <v>Deportista</v>
@@ -6067,13 +6067,13 @@
         <v>50m</v>
       </c>
       <c r="K129" t="str">
-        <v>Electrónico</v>
+        <v>Manual</v>
       </c>
       <c r="L129" t="str">
-        <v>I Trofeo Federación 226ERS piscina 50m</v>
+        <v>Control Libre Infantil y 7ª Control Junior y Absoluto Valencia</v>
       </c>
       <c r="M129" t="str">
-        <v>Castellón</v>
+        <v>Sedavi</v>
       </c>
       <c r="N129" t="str">
         <v>No</v>
@@ -6081,28 +6081,28 @@
     </row>
     <row r="130">
       <c r="A130">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="B130" t="str">
-        <v>400 Libre</v>
+        <v>200 Libre</v>
       </c>
       <c r="C130" t="str">
-        <v>ARIADNA MANZANEDA GARCIA</v>
+        <v>IRENE BELLVER OJEDA</v>
       </c>
       <c r="D130">
-        <v>2012</v>
+        <v>2009</v>
       </c>
       <c r="E130" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F130" t="str">
-        <v>00:05:12.37</v>
+        <v>00:03:33.92</v>
       </c>
       <c r="G130">
-        <v>428</v>
+        <v>144</v>
       </c>
       <c r="H130" s="1">
-        <v>46172.99949074074</v>
+        <v>44612.99949074074</v>
       </c>
       <c r="I130" t="str">
         <v>Deportista</v>
@@ -6114,10 +6114,10 @@
         <v>Manual</v>
       </c>
       <c r="L130" t="str">
-        <v>LVI TROFEU SANT PASCUAL XXXVII MEMORIAL JOSE VICENTE MARTI BARRACHINA</v>
+        <v>4º Control Infantil Junior y Absoluto Castellón</v>
       </c>
       <c r="M130" t="str">
-        <v>Vila-Real</v>
+        <v>Castellón</v>
       </c>
       <c r="N130" t="str">
         <v>No</v>
@@ -6125,28 +6125,28 @@
     </row>
     <row r="131">
       <c r="A131">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B131" t="str">
         <v>400 Libre</v>
       </c>
       <c r="C131" t="str">
-        <v>SOFIA CALABUIG MARTINEZ</v>
+        <v>ISABEL MORAGUES GINER</v>
       </c>
       <c r="D131">
-        <v>2011</v>
+        <v>2005</v>
       </c>
       <c r="E131" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F131" t="str">
-        <v>00:05:13.97</v>
+        <v>00:04:57.74</v>
       </c>
       <c r="G131">
-        <v>421</v>
+        <v>494</v>
       </c>
       <c r="H131" s="1">
-        <v>45711.99949074074</v>
+        <v>45682.99949074074</v>
       </c>
       <c r="I131" t="str">
         <v>Deportista</v>
@@ -6158,39 +6158,39 @@
         <v>Electrónico</v>
       </c>
       <c r="L131" t="str">
-        <v>CAMPEONATO AUTONOMICO INFANTIL DE INVIERNO 2025 C.V.</v>
+        <v>XXX MEMORIAL PASCUAL ROMAN</v>
       </c>
       <c r="M131" t="str">
-        <v>ELCHE</v>
+        <v>Elche</v>
       </c>
       <c r="N131" t="str">
-        <v>Sí</v>
+        <v>No</v>
       </c>
     </row>
     <row r="132">
       <c r="A132">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B132" t="str">
         <v>400 Libre</v>
       </c>
       <c r="C132" t="str">
-        <v>INES PEDRERO MARTINEZ</v>
+        <v>ALBA IZQUIERDO LOPEZ</v>
       </c>
       <c r="D132">
-        <v>2008</v>
+        <v>2003</v>
       </c>
       <c r="E132" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F132" t="str">
-        <v>00:05:14.20</v>
+        <v>00:05:07.72</v>
       </c>
       <c r="G132">
-        <v>420</v>
+        <v>448</v>
       </c>
       <c r="H132" s="1">
-        <v>45493.99949074074</v>
+        <v>45094.99949074074</v>
       </c>
       <c r="I132" t="str">
         <v>Deportista</v>
@@ -6202,7 +6202,7 @@
         <v>Electrónico</v>
       </c>
       <c r="L132" t="str">
-        <v>Campeonato Autonómico Open Junior Y Absoluto de Verano</v>
+        <v>I Trofeo Federación 226ERS piscina 50m</v>
       </c>
       <c r="M132" t="str">
         <v>Castellón</v>
@@ -6213,28 +6213,28 @@
     </row>
     <row r="133">
       <c r="A133">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B133" t="str">
         <v>400 Libre</v>
       </c>
       <c r="C133" t="str">
-        <v>MANUELA RADEANU</v>
+        <v>MARIA ANGELES GRASSO CUENCA</v>
       </c>
       <c r="D133">
-        <v>2007</v>
+        <v>2011</v>
       </c>
       <c r="E133" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F133" t="str">
-        <v>00:05:16.47</v>
+        <v>00:05:10.36</v>
       </c>
       <c r="G133">
-        <v>411</v>
+        <v>436</v>
       </c>
       <c r="H133" s="1">
-        <v>44381.99949074074</v>
+        <v>46200.99949074074</v>
       </c>
       <c r="I133" t="str">
         <v>Deportista</v>
@@ -6246,10 +6246,10 @@
         <v>Electrónico</v>
       </c>
       <c r="L133" t="str">
-        <v>Autonomico Infantil Verano</v>
+        <v>CAMPEONATO AUTONOMICO INFANTIL DE VERANO DE LA C.V. 2026</v>
       </c>
       <c r="M133" t="str">
-        <v>Castellon</v>
+        <v>CASTELLON</v>
       </c>
       <c r="N133" t="str">
         <v>No</v>
@@ -6257,28 +6257,28 @@
     </row>
     <row r="134">
       <c r="A134">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B134" t="str">
         <v>400 Libre</v>
       </c>
       <c r="C134" t="str">
-        <v>MARIA ANGELES GRASSO CUENCA</v>
+        <v>ARIADNA MANZANEDA GARCIA</v>
       </c>
       <c r="D134">
-        <v>2011</v>
+        <v>2012</v>
       </c>
       <c r="E134" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F134" t="str">
-        <v>00:05:16.71</v>
+        <v>00:05:11.76</v>
       </c>
       <c r="G134">
-        <v>411</v>
+        <v>430</v>
       </c>
       <c r="H134" s="1">
-        <v>46144.99949074074</v>
+        <v>46200.99949074074</v>
       </c>
       <c r="I134" t="str">
         <v>Deportista</v>
@@ -6290,10 +6290,10 @@
         <v>Electrónico</v>
       </c>
       <c r="L134" t="str">
-        <v>XX TROFEO INTERNACIONAL IBERCAJA CIUDAD ZARAGOZA 2026 XVII MEMORIAL EDUARDO LASTRADA</v>
+        <v>CAMPEONATO AUTONOMICO INFANTIL DE VERANO DE LA C.V. 2026</v>
       </c>
       <c r="M134" t="str">
-        <v>ZARAGOZA (C)</v>
+        <v>CASTELLON</v>
       </c>
       <c r="N134" t="str">
         <v>No</v>
@@ -6301,28 +6301,28 @@
     </row>
     <row r="135">
       <c r="A135">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B135" t="str">
         <v>400 Libre</v>
       </c>
       <c r="C135" t="str">
-        <v>CAMILA GUEVARA PEROZO</v>
+        <v>SOFIA CALABUIG MARTINEZ</v>
       </c>
       <c r="D135">
-        <v>2010</v>
+        <v>2011</v>
       </c>
       <c r="E135" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F135" t="str">
-        <v>00:05:28.06</v>
+        <v>00:05:13.97</v>
       </c>
       <c r="G135">
-        <v>369</v>
+        <v>421</v>
       </c>
       <c r="H135" s="1">
-        <v>45836.99949074074</v>
+        <v>45711.99949074074</v>
       </c>
       <c r="I135" t="str">
         <v>Deportista</v>
@@ -6334,39 +6334,39 @@
         <v>Electrónico</v>
       </c>
       <c r="L135" t="str">
-        <v>CAMPEONATO AUTONOMICO INFANTIL DE VERANO 2025</v>
+        <v>CAMPEONATO AUTONOMICO INFANTIL DE INVIERNO 2025 C.V.</v>
       </c>
       <c r="M135" t="str">
-        <v>Castellón</v>
+        <v>ELCHE</v>
       </c>
       <c r="N135" t="str">
-        <v>No</v>
+        <v>Sí</v>
       </c>
     </row>
     <row r="136">
       <c r="A136">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B136" t="str">
         <v>400 Libre</v>
       </c>
       <c r="C136" t="str">
-        <v>APPOLINARIIA KOROLEVA</v>
+        <v>INES PEDRERO MARTINEZ</v>
       </c>
       <c r="D136">
-        <v>2011</v>
+        <v>2008</v>
       </c>
       <c r="E136" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F136" t="str">
-        <v>00:05:33.89</v>
+        <v>00:05:14.20</v>
       </c>
       <c r="G136">
-        <v>350</v>
+        <v>420</v>
       </c>
       <c r="H136" s="1">
-        <v>45710.99949074074</v>
+        <v>45493.99949074074</v>
       </c>
       <c r="I136" t="str">
         <v>Deportista</v>
@@ -6378,10 +6378,10 @@
         <v>Electrónico</v>
       </c>
       <c r="L136" t="str">
-        <v>CAMPEONATO AUTONOMICO INFANTIL DE INVIERNO 2025 C.V.</v>
+        <v>Campeonato Autonómico Open Junior Y Absoluto de Verano</v>
       </c>
       <c r="M136" t="str">
-        <v>ELCHE</v>
+        <v>Castellón</v>
       </c>
       <c r="N136" t="str">
         <v>No</v>
@@ -6389,28 +6389,28 @@
     </row>
     <row r="137">
       <c r="A137">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B137" t="str">
         <v>400 Libre</v>
       </c>
       <c r="C137" t="str">
-        <v>MARIA MENDOZA GOMEZ</v>
+        <v>MANUELA RADEANU</v>
       </c>
       <c r="D137">
-        <v>2003</v>
+        <v>2007</v>
       </c>
       <c r="E137" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F137" t="str">
-        <v>00:05:36.72</v>
+        <v>00:05:16.47</v>
       </c>
       <c r="G137">
-        <v>342</v>
+        <v>411</v>
       </c>
       <c r="H137" s="1">
-        <v>43638.99949074074</v>
+        <v>44381.99949074074</v>
       </c>
       <c r="I137" t="str">
         <v>Deportista</v>
@@ -6419,13 +6419,13 @@
         <v>50m</v>
       </c>
       <c r="K137" t="str">
-        <v>Manual</v>
+        <v>Electrónico</v>
       </c>
       <c r="L137" t="str">
-        <v>7ª Jornada Control infa y mayores</v>
+        <v>Autonomico Infantil Verano</v>
       </c>
       <c r="M137" t="str">
-        <v>Moncada</v>
+        <v>Castellon</v>
       </c>
       <c r="N137" t="str">
         <v>No</v>
@@ -6433,28 +6433,28 @@
     </row>
     <row r="138">
       <c r="A138">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B138" t="str">
         <v>400 Libre</v>
       </c>
       <c r="C138" t="str">
-        <v>ROCIO MARTINEZ GONZALEZ</v>
+        <v>CAMILA GUEVARA PEROZO</v>
       </c>
       <c r="D138">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="E138" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F138" t="str">
-        <v>00:05:43.89</v>
+        <v>00:05:28.06</v>
       </c>
       <c r="G138">
-        <v>321</v>
+        <v>369</v>
       </c>
       <c r="H138" s="1">
-        <v>45681.99949074074</v>
+        <v>45836.99949074074</v>
       </c>
       <c r="I138" t="str">
         <v>Deportista</v>
@@ -6466,39 +6466,39 @@
         <v>Electrónico</v>
       </c>
       <c r="L138" t="str">
-        <v>XXX MEMORIAL PASCUAL ROMAN</v>
+        <v>CAMPEONATO AUTONOMICO INFANTIL DE VERANO 2025</v>
       </c>
       <c r="M138" t="str">
-        <v>Elche</v>
+        <v>Castellón</v>
       </c>
       <c r="N138" t="str">
-        <v>Sí</v>
+        <v>No</v>
       </c>
     </row>
     <row r="139">
       <c r="A139">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B139" t="str">
         <v>400 Libre</v>
       </c>
       <c r="C139" t="str">
-        <v>PAOLA MEIJIDE VILLANUEVA</v>
+        <v>APPOLINARIIA KOROLEVA</v>
       </c>
       <c r="D139">
-        <v>2010</v>
+        <v>2011</v>
       </c>
       <c r="E139" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F139" t="str">
-        <v>00:05:59.38</v>
+        <v>00:05:33.89</v>
       </c>
       <c r="G139">
-        <v>281</v>
+        <v>350</v>
       </c>
       <c r="H139" s="1">
-        <v>46172.99949074074</v>
+        <v>45710.99949074074</v>
       </c>
       <c r="I139" t="str">
         <v>Deportista</v>
@@ -6507,13 +6507,13 @@
         <v>50m</v>
       </c>
       <c r="K139" t="str">
-        <v>Manual</v>
+        <v>Electrónico</v>
       </c>
       <c r="L139" t="str">
-        <v>LVI TROFEU SANT PASCUAL XXXVII MEMORIAL JOSE VICENTE MARTI BARRACHINA</v>
+        <v>CAMPEONATO AUTONOMICO INFANTIL DE INVIERNO 2025 C.V.</v>
       </c>
       <c r="M139" t="str">
-        <v>Vila-Real</v>
+        <v>ELCHE</v>
       </c>
       <c r="N139" t="str">
         <v>No</v>
@@ -6521,28 +6521,28 @@
     </row>
     <row r="140">
       <c r="A140">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B140" t="str">
         <v>400 Libre</v>
       </c>
       <c r="C140" t="str">
-        <v>SANDRA DOMINGUEZ VALERO</v>
+        <v>MARIA MENDOZA GOMEZ</v>
       </c>
       <c r="D140">
-        <v>2007</v>
+        <v>2003</v>
       </c>
       <c r="E140" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F140" t="str">
-        <v>00:06:26.63</v>
+        <v>00:05:36.72</v>
       </c>
       <c r="G140">
-        <v>226</v>
+        <v>342</v>
       </c>
       <c r="H140" s="1">
-        <v>44366.99949074074</v>
+        <v>43638.99949074074</v>
       </c>
       <c r="I140" t="str">
         <v>Deportista</v>
@@ -6554,10 +6554,10 @@
         <v>Manual</v>
       </c>
       <c r="L140" t="str">
-        <v>PRUEBAS DE ACCESO AUTONÓMICO INFANTIL Y MAYORES 3 CASTELLON</v>
+        <v>7ª Jornada Control infa y mayores</v>
       </c>
       <c r="M140" t="str">
-        <v>CASTELLON</v>
+        <v>Moncada</v>
       </c>
       <c r="N140" t="str">
         <v>No</v>
@@ -6565,28 +6565,28 @@
     </row>
     <row r="141">
       <c r="A141">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B141" t="str">
         <v>400 Libre</v>
       </c>
       <c r="C141" t="str">
-        <v>AINOHA MONASTERIO BANEGA</v>
+        <v>ROCIO MARTINEZ GONZALEZ</v>
       </c>
       <c r="D141">
-        <v>2007</v>
+        <v>2011</v>
       </c>
       <c r="E141" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F141" t="str">
-        <v>00:07:18.75</v>
+        <v>00:05:43.89</v>
       </c>
       <c r="G141">
-        <v>154</v>
+        <v>321</v>
       </c>
       <c r="H141" s="1">
-        <v>44611.99949074074</v>
+        <v>45681.99949074074</v>
       </c>
       <c r="I141" t="str">
         <v>Deportista</v>
@@ -6595,42 +6595,42 @@
         <v>50m</v>
       </c>
       <c r="K141" t="str">
-        <v>Manual</v>
+        <v>Electrónico</v>
       </c>
       <c r="L141" t="str">
-        <v>4º Control Infantil Junior y Absoluto Castellón</v>
+        <v>XXX MEMORIAL PASCUAL ROMAN</v>
       </c>
       <c r="M141" t="str">
-        <v>Castellón</v>
+        <v>Elche</v>
       </c>
       <c r="N141" t="str">
-        <v>No</v>
+        <v>Sí</v>
       </c>
     </row>
     <row r="142">
       <c r="A142">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="B142" t="str">
-        <v>800 Libre</v>
+        <v>400 Libre</v>
       </c>
       <c r="C142" t="str">
-        <v>ISABEL MORAGUES GINER</v>
+        <v>PAOLA MEIJIDE VILLANUEVA</v>
       </c>
       <c r="D142">
-        <v>2005</v>
+        <v>2010</v>
       </c>
       <c r="E142" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F142" t="str">
-        <v>00:10:11.75</v>
+        <v>00:05:59.38</v>
       </c>
       <c r="G142">
-        <v>498</v>
+        <v>281</v>
       </c>
       <c r="H142" s="1">
-        <v>45681.99949074074</v>
+        <v>46172.99949074074</v>
       </c>
       <c r="I142" t="str">
         <v>Deportista</v>
@@ -6639,13 +6639,13 @@
         <v>50m</v>
       </c>
       <c r="K142" t="str">
-        <v>Electrónico</v>
+        <v>Manual</v>
       </c>
       <c r="L142" t="str">
-        <v>XXX MEMORIAL PASCUAL ROMAN</v>
+        <v>LVI TROFEU SANT PASCUAL XXXVII MEMORIAL JOSE VICENTE MARTI BARRACHINA</v>
       </c>
       <c r="M142" t="str">
-        <v>Elche</v>
+        <v>Vila-Real</v>
       </c>
       <c r="N142" t="str">
         <v>No</v>
@@ -6653,28 +6653,28 @@
     </row>
     <row r="143">
       <c r="A143">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="B143" t="str">
-        <v>800 Libre</v>
+        <v>400 Libre</v>
       </c>
       <c r="C143" t="str">
-        <v>SOFIA CALABUIG MARTINEZ</v>
+        <v>SANDRA DOMINGUEZ VALERO</v>
       </c>
       <c r="D143">
-        <v>2011</v>
+        <v>2007</v>
       </c>
       <c r="E143" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F143" t="str">
-        <v>00:10:39.01</v>
+        <v>00:06:26.63</v>
       </c>
       <c r="G143">
-        <v>437</v>
+        <v>226</v>
       </c>
       <c r="H143" s="1">
-        <v>45711.99949074074</v>
+        <v>44366.99949074074</v>
       </c>
       <c r="I143" t="str">
         <v>Deportista</v>
@@ -6683,13 +6683,13 @@
         <v>50m</v>
       </c>
       <c r="K143" t="str">
-        <v>Electrónico</v>
+        <v>Manual</v>
       </c>
       <c r="L143" t="str">
-        <v>CAMPEONATO AUTONOMICO INFANTIL DE INVIERNO 2025 C.V.</v>
+        <v>PRUEBAS DE ACCESO AUTONÓMICO INFANTIL Y MAYORES 3 CASTELLON</v>
       </c>
       <c r="M143" t="str">
-        <v>ELCHE</v>
+        <v>CASTELLON</v>
       </c>
       <c r="N143" t="str">
         <v>No</v>
@@ -6697,28 +6697,28 @@
     </row>
     <row r="144">
       <c r="A144">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="B144" t="str">
-        <v>800 Libre</v>
+        <v>400 Libre</v>
       </c>
       <c r="C144" t="str">
-        <v>ALBA IZQUIERDO LOPEZ</v>
+        <v>AINOHA MONASTERIO BANEGA</v>
       </c>
       <c r="D144">
-        <v>2003</v>
+        <v>2007</v>
       </c>
       <c r="E144" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F144" t="str">
-        <v>00:10:47.40</v>
+        <v>00:07:18.75</v>
       </c>
       <c r="G144">
-        <v>420</v>
+        <v>154</v>
       </c>
       <c r="H144" s="1">
-        <v>44974.99949074074</v>
+        <v>44611.99949074074</v>
       </c>
       <c r="I144" t="str">
         <v>Deportista</v>
@@ -6727,13 +6727,13 @@
         <v>50m</v>
       </c>
       <c r="K144" t="str">
-        <v>Electrónico</v>
+        <v>Manual</v>
       </c>
       <c r="L144" t="str">
-        <v>Trofeo Internacional XXVIII Memorial Pascual Roman</v>
+        <v>4º Control Infantil Junior y Absoluto Castellón</v>
       </c>
       <c r="M144" t="str">
-        <v>Elche</v>
+        <v>Castellón</v>
       </c>
       <c r="N144" t="str">
         <v>No</v>
@@ -6741,28 +6741,28 @@
     </row>
     <row r="145">
       <c r="A145">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B145" t="str">
         <v>800 Libre</v>
       </c>
       <c r="C145" t="str">
-        <v>ARIADNA MANZANEDA GARCIA</v>
+        <v>ISABEL MORAGUES GINER</v>
       </c>
       <c r="D145">
-        <v>2012</v>
+        <v>2005</v>
       </c>
       <c r="E145" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F145" t="str">
-        <v>00:10:52.11</v>
+        <v>00:10:11.75</v>
       </c>
       <c r="G145">
-        <v>411</v>
+        <v>498</v>
       </c>
       <c r="H145" s="1">
-        <v>46082.99949074074</v>
+        <v>45681.99949074074</v>
       </c>
       <c r="I145" t="str">
         <v>Deportista</v>
@@ -6774,10 +6774,10 @@
         <v>Electrónico</v>
       </c>
       <c r="L145" t="str">
-        <v>CAMPEONATO AUTONOMICO INFANTIL DE INVIERNO 2026</v>
+        <v>XXX MEMORIAL PASCUAL ROMAN</v>
       </c>
       <c r="M145" t="str">
-        <v>CASTELLÓN</v>
+        <v>Elche</v>
       </c>
       <c r="N145" t="str">
         <v>No</v>
@@ -6785,28 +6785,28 @@
     </row>
     <row r="146">
       <c r="A146">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B146" t="str">
         <v>800 Libre</v>
       </c>
       <c r="C146" t="str">
-        <v>MANUELA RADEANU</v>
+        <v>SOFIA CALABUIG MARTINEZ</v>
       </c>
       <c r="D146">
-        <v>2007</v>
+        <v>2011</v>
       </c>
       <c r="E146" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F146" t="str">
-        <v>00:11:23.46</v>
+        <v>00:10:39.01</v>
       </c>
       <c r="G146">
-        <v>357</v>
+        <v>437</v>
       </c>
       <c r="H146" s="1">
-        <v>44367.99949074074</v>
+        <v>45711.99949074074</v>
       </c>
       <c r="I146" t="str">
         <v>Deportista</v>
@@ -6815,13 +6815,13 @@
         <v>50m</v>
       </c>
       <c r="K146" t="str">
-        <v>Manual</v>
+        <v>Electrónico</v>
       </c>
       <c r="L146" t="str">
-        <v>PRUEBAS DE ACCESO AUTONÓMICO INFANTIL Y MAYORES 3 CASTELLON</v>
+        <v>CAMPEONATO AUTONOMICO INFANTIL DE INVIERNO 2025 C.V.</v>
       </c>
       <c r="M146" t="str">
-        <v>CASTELLON</v>
+        <v>ELCHE</v>
       </c>
       <c r="N146" t="str">
         <v>No</v>
@@ -6829,28 +6829,28 @@
     </row>
     <row r="147">
       <c r="A147">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B147" t="str">
         <v>800 Libre</v>
       </c>
       <c r="C147" t="str">
-        <v>ROCIO MARTINEZ GONZALEZ</v>
+        <v>ARIADNA MANZANEDA GARCIA</v>
       </c>
       <c r="D147">
-        <v>2011</v>
+        <v>2012</v>
       </c>
       <c r="E147" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F147" t="str">
-        <v>00:11:46.66</v>
+        <v>00:10:44.25</v>
       </c>
       <c r="G147">
-        <v>323</v>
+        <v>426</v>
       </c>
       <c r="H147" s="1">
-        <v>45681.99949074074</v>
+        <v>46201.99949074074</v>
       </c>
       <c r="I147" t="str">
         <v>Deportista</v>
@@ -6862,10 +6862,10 @@
         <v>Electrónico</v>
       </c>
       <c r="L147" t="str">
-        <v>XXX MEMORIAL PASCUAL ROMAN</v>
+        <v>CAMPEONATO AUTONOMICO INFANTIL DE VERANO DE LA C.V. 2026</v>
       </c>
       <c r="M147" t="str">
-        <v>Elche</v>
+        <v>CASTELLON</v>
       </c>
       <c r="N147" t="str">
         <v>No</v>
@@ -6873,28 +6873,28 @@
     </row>
     <row r="148">
       <c r="A148">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B148" t="str">
         <v>800 Libre</v>
       </c>
       <c r="C148" t="str">
-        <v>APPOLINARIIA KOROLEVA</v>
+        <v>ALBA IZQUIERDO LOPEZ</v>
       </c>
       <c r="D148">
-        <v>2011</v>
+        <v>2003</v>
       </c>
       <c r="E148" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F148" t="str">
-        <v>00:12:12.68</v>
+        <v>00:10:47.40</v>
       </c>
       <c r="G148">
-        <v>290</v>
+        <v>420</v>
       </c>
       <c r="H148" s="1">
-        <v>45681.99949074074</v>
+        <v>44974.99949074074</v>
       </c>
       <c r="I148" t="str">
         <v>Deportista</v>
@@ -6906,7 +6906,7 @@
         <v>Electrónico</v>
       </c>
       <c r="L148" t="str">
-        <v>XXX MEMORIAL PASCUAL ROMAN</v>
+        <v>Trofeo Internacional XXVIII Memorial Pascual Roman</v>
       </c>
       <c r="M148" t="str">
         <v>Elche</v>
@@ -6917,13 +6917,13 @@
     </row>
     <row r="149">
       <c r="A149">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B149" t="str">
         <v>800 Libre</v>
       </c>
       <c r="C149" t="str">
-        <v>SANDRA DOMINGUEZ VALERO</v>
+        <v>MANUELA RADEANU</v>
       </c>
       <c r="D149">
         <v>2007</v>
@@ -6932,10 +6932,10 @@
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F149" t="str">
-        <v>00:13:16.04</v>
+        <v>00:11:23.46</v>
       </c>
       <c r="G149">
-        <v>226</v>
+        <v>357</v>
       </c>
       <c r="H149" s="1">
         <v>44367.99949074074</v>
@@ -6961,13 +6961,13 @@
     </row>
     <row r="150">
       <c r="A150">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="B150" t="str">
-        <v>1500 Libre</v>
+        <v>800 Libre</v>
       </c>
       <c r="C150" t="str">
-        <v>SOFIA CALABUIG MARTINEZ</v>
+        <v>ROCIO MARTINEZ GONZALEZ</v>
       </c>
       <c r="D150">
         <v>2011</v>
@@ -6976,36 +6976,212 @@
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F150" t="str">
+        <v>00:11:46.66</v>
+      </c>
+      <c r="G150">
+        <v>323</v>
+      </c>
+      <c r="H150" s="1">
+        <v>45681.99949074074</v>
+      </c>
+      <c r="I150" t="str">
+        <v>Deportista</v>
+      </c>
+      <c r="J150" t="str">
+        <v>50m</v>
+      </c>
+      <c r="K150" t="str">
+        <v>Electrónico</v>
+      </c>
+      <c r="L150" t="str">
+        <v>XXX MEMORIAL PASCUAL ROMAN</v>
+      </c>
+      <c r="M150" t="str">
+        <v>Elche</v>
+      </c>
+      <c r="N150" t="str">
+        <v>No</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151">
+        <v>7</v>
+      </c>
+      <c r="B151" t="str">
+        <v>800 Libre</v>
+      </c>
+      <c r="C151" t="str">
+        <v>APPOLINARIIA KOROLEVA</v>
+      </c>
+      <c r="D151">
+        <v>2011</v>
+      </c>
+      <c r="E151" t="str">
+        <v>C.N. MEDITERRANEO VALENCIA</v>
+      </c>
+      <c r="F151" t="str">
+        <v>00:12:12.68</v>
+      </c>
+      <c r="G151">
+        <v>290</v>
+      </c>
+      <c r="H151" s="1">
+        <v>45681.99949074074</v>
+      </c>
+      <c r="I151" t="str">
+        <v>Deportista</v>
+      </c>
+      <c r="J151" t="str">
+        <v>50m</v>
+      </c>
+      <c r="K151" t="str">
+        <v>Electrónico</v>
+      </c>
+      <c r="L151" t="str">
+        <v>XXX MEMORIAL PASCUAL ROMAN</v>
+      </c>
+      <c r="M151" t="str">
+        <v>Elche</v>
+      </c>
+      <c r="N151" t="str">
+        <v>No</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152">
+        <v>8</v>
+      </c>
+      <c r="B152" t="str">
+        <v>800 Libre</v>
+      </c>
+      <c r="C152" t="str">
+        <v>SANDRA DOMINGUEZ VALERO</v>
+      </c>
+      <c r="D152">
+        <v>2007</v>
+      </c>
+      <c r="E152" t="str">
+        <v>C.N. MEDITERRANEO VALENCIA</v>
+      </c>
+      <c r="F152" t="str">
+        <v>00:13:16.04</v>
+      </c>
+      <c r="G152">
+        <v>226</v>
+      </c>
+      <c r="H152" s="1">
+        <v>44367.99949074074</v>
+      </c>
+      <c r="I152" t="str">
+        <v>Deportista</v>
+      </c>
+      <c r="J152" t="str">
+        <v>50m</v>
+      </c>
+      <c r="K152" t="str">
+        <v>Manual</v>
+      </c>
+      <c r="L152" t="str">
+        <v>PRUEBAS DE ACCESO AUTONÓMICO INFANTIL Y MAYORES 3 CASTELLON</v>
+      </c>
+      <c r="M152" t="str">
+        <v>CASTELLON</v>
+      </c>
+      <c r="N152" t="str">
+        <v>No</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153">
+        <v>1</v>
+      </c>
+      <c r="B153" t="str">
+        <v>1500 Libre</v>
+      </c>
+      <c r="C153" t="str">
+        <v>SOFIA CALABUIG MARTINEZ</v>
+      </c>
+      <c r="D153">
+        <v>2011</v>
+      </c>
+      <c r="E153" t="str">
+        <v>C.N. MEDITERRANEO VALENCIA</v>
+      </c>
+      <c r="F153" t="str">
         <v>00:20:28.40</v>
       </c>
-      <c r="G150">
+      <c r="G153">
         <v>421</v>
       </c>
-      <c r="H150" s="1">
+      <c r="H153" s="1">
         <v>45710.99949074074</v>
       </c>
-      <c r="I150" t="str">
-        <v>Deportista</v>
-      </c>
-      <c r="J150" t="str">
-        <v>50m</v>
-      </c>
-      <c r="K150" t="str">
-        <v>Electrónico</v>
-      </c>
-      <c r="L150" t="str">
+      <c r="I153" t="str">
+        <v>Deportista</v>
+      </c>
+      <c r="J153" t="str">
+        <v>50m</v>
+      </c>
+      <c r="K153" t="str">
+        <v>Electrónico</v>
+      </c>
+      <c r="L153" t="str">
         <v>CAMPEONATO AUTONOMICO INFANTIL DE INVIERNO 2025 C.V.</v>
       </c>
-      <c r="M150" t="str">
+      <c r="M153" t="str">
         <v>ELCHE</v>
       </c>
-      <c r="N150" t="str">
+      <c r="N153" t="str">
+        <v>No</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154">
+        <v>2</v>
+      </c>
+      <c r="B154" t="str">
+        <v>1500 Libre</v>
+      </c>
+      <c r="C154" t="str">
+        <v>ARIADNA MANZANEDA GARCIA</v>
+      </c>
+      <c r="D154">
+        <v>2012</v>
+      </c>
+      <c r="E154" t="str">
+        <v>C.N. MEDITERRANEO VALENCIA</v>
+      </c>
+      <c r="F154" t="str">
+        <v>00:20:33.43</v>
+      </c>
+      <c r="G154">
+        <v>416</v>
+      </c>
+      <c r="H154" s="1">
+        <v>46200.99949074074</v>
+      </c>
+      <c r="I154" t="str">
+        <v>Deportista</v>
+      </c>
+      <c r="J154" t="str">
+        <v>50m</v>
+      </c>
+      <c r="K154" t="str">
+        <v>Electrónico</v>
+      </c>
+      <c r="L154" t="str">
+        <v>CAMPEONATO AUTONOMICO INFANTIL DE VERANO DE LA C.V. 2026</v>
+      </c>
+      <c r="M154" t="str">
+        <v>CASTELLON</v>
+      </c>
+      <c r="N154" t="str">
         <v>No</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:O150"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:O154"/>
   </ignoredErrors>
 </worksheet>
 </file>